--- a/artifacts/traceability_reports/primary_source_requirements.xlsx
+++ b/artifacts/traceability_reports/primary_source_requirements.xlsx
@@ -9,9 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary Source Requirements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upstream Coverage" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirement Presence" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Primary Source Requirements'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Upstream Coverage'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Requirement Presence'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -62,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -72,6 +78,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -170,6 +177,51 @@
     <tableColumn id="16" name="operating_mode"/>
     <tableColumn id="17" name="parameter_signal_register"/>
     <tableColumn id="18" name="value_range_condition"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ReportData2" displayName="ReportData2" ref="A1:P11" headerRowCount="1">
+  <autoFilter ref="A1:P11"/>
+  <tableColumns count="16">
+    <tableColumn id="1" name="covering_level"/>
+    <tableColumn id="2" name="covering_block"/>
+    <tableColumn id="3" name="covered_upstream_level"/>
+    <tableColumn id="4" name="covered_upstream_block"/>
+    <tableColumn id="5" name="denominator_scope"/>
+    <tableColumn id="6" name="covered_unique_upstream_requirements"/>
+    <tableColumn id="7" name="total_unique_upstream_requirements"/>
+    <tableColumn id="8" name="uncovered_upstream_requirements"/>
+    <tableColumn id="9" name="coverage_percentage"/>
+    <tableColumn id="10" name="coverage_status"/>
+    <tableColumn id="11" name="coverage_basis"/>
+    <tableColumn id="12" name="covered_upstream_requirement_ids"/>
+    <tableColumn id="13" name="uncovered_upstream_requirement_ids"/>
+    <tableColumn id="14" name="snapshot_id"/>
+    <tableColumn id="15" name="covering_node_id"/>
+    <tableColumn id="16" name="covered_upstream_node_id"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ReportData3" displayName="ReportData3" ref="A1:K2" headerRowCount="1">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="hierarchy_level"/>
+    <tableColumn id="2" name="block"/>
+    <tableColumn id="3" name="scope"/>
+    <tableColumn id="4" name="expected_requirements"/>
+    <tableColumn id="5" name="represented_requirements"/>
+    <tableColumn id="6" name="missing_requirements"/>
+    <tableColumn id="7" name="presence_percentage"/>
+    <tableColumn id="8" name="presence_status"/>
+    <tableColumn id="9" name="coverage_basis"/>
+    <tableColumn id="10" name="missing_requirement_ids"/>
+    <tableColumn id="11" name="snapshot_id"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11194,12 +11246,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0014</t>
+          <t>DDS_STBIO1_395</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0014</t>
+          <t>DDS_STBIO1_395</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -11210,22 +11262,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>The BOOT routine shall starts when the OTP_BOOT bit rises and shall completes when quokka_boot_end rises. [Vpriority High]</t>
+          <t>DCC IP 00 25nA 01 50nA 10 100nA 11 200nA 000 C</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 004 (page 90)</t>
+          <t>Section 13.1.2.2 Requirements (under Section 13.1.2 PAD Mux), paragraph 033 (page 71)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ADSP</t>
+          <t>PAD MUX</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11240,7 +11292,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0014 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_395 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11270,12 +11322,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0015</t>
+          <t>DDS_STBIO1_0014</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0015</t>
+          <t>DDS_STBIO1_0014</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -11286,7 +11338,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>During OTP boot operation, the ADSP shall copy the content of the OTP memory into the OTP registers, following the procedure to access OTP memory [Vpriority High]</t>
+          <t>The BOOT routine shall starts when the OTP_BOOT bit rises and shall completes when quokka_boot_end rises. [Vpriority High]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11296,7 +11348,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 012 (page 90)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 004 (page 90)</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11316,7 +11368,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0015 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0014 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11346,12 +11398,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0016</t>
+          <t>DDS_STBIO1_0015</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0016</t>
+          <t>DDS_STBIO1_0015</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -11362,7 +11414,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>During BOOT routine, ADSP shall first read the last location of the OTP memory, at address 0x7F. If the content is 0xFF, called “lifecycle” byte, then the READ operation proceeds from address 0 to address 0x2F; otherwise, ADSP shall not perform any further reads.</t>
+          <t>During OTP boot operation, the ADSP shall copy the content of the OTP memory into the OTP registers, following the procedure to access OTP memory [Vpriority High]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -11372,7 +11424,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 019 (page 90)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 012 (page 90)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11392,7 +11444,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0016 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0015 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11416,22 +11468,18 @@
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
+      <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0017</t>
+          <t>DDS_STBIO1_0016</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0017</t>
+          <t>DDS_STBIO1_0016</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -11442,7 +11490,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>To perform a BOOT routine, OTP_BOOT bit shall be written when quokka_run is low. [Vpriority High]</t>
+          <t>During BOOT routine, ADSP shall first read the last location of the OTP memory, at address 0x7F. If the content is 0xFF, called “lifecycle” byte, then the READ operation proceeds from address 0 to address 0x2F; otherwise, ADSP shall not perform any further reads. Figure 12: Boot Routine [Vpriority High]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -11452,7 +11500,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 009 (page 91)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 019 (page 90)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11472,7 +11520,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0017 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0016 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.95</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11496,18 +11544,22 @@
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
       <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0018</t>
+          <t>DDS_STBIO1_0017</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0018</t>
+          <t>DDS_STBIO1_0017</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -11518,7 +11570,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>The WRITE routine shall start when OTP Write Bit rises and completes when quokka_run falls. [Vpriority High]</t>
+          <t>To perform a BOOT routine, OTP_BOOT bit shall be written when quokka_run is low. [Vpriority High]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11528,7 +11580,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 013 (page 91)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 009 (page 91)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11548,7 +11600,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0018 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0017 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11578,12 +11630,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0019</t>
+          <t>DDS_STBIO1_0018</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0019</t>
+          <t>DDS_STBIO1_0018</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -11594,7 +11646,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>During WRITE routine ADSP shall copy the content of the OTP regmap into the OTP memory, following the procedure to burn the fuses as expressed in the OTP datasheet [Vpriority High]</t>
+          <t>The WRITE routine shall start when OTP Write Bit rises and completes when quokka_run falls. [Vpriority High]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -11604,7 +11656,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 017 (page 91)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 013 (page 91)</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11624,7 +11676,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0019 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0018 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11654,12 +11706,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0020</t>
+          <t>DDS_STBIO1_0019</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0020</t>
+          <t>DDS_STBIO1_0019</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -11670,7 +11722,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>During WRITE routine, ADSP shall allow copying all OTP Registers into the OTP Memory only if the location 0x24 of OTP Memory (OTP[24] in the following diagram) is not set to 0xFF.</t>
+          <t>During WRITE routine ADSP shall copy the content of the OTP regmap into the OTP memory, following the procedure to burn the fuses as expressed in the OTP datasheet [Vpriority High]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -11680,7 +11732,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 008 (page 92)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 017 (page 91)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11700,7 +11752,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0020 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0019 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11730,12 +11782,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0021</t>
+          <t>DDS_STBIO1_0020</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0021</t>
+          <t>DDS_STBIO1_0020</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -11746,7 +11798,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>During the WRITE routine and after copying all OTP Registers into the OTP Memory, ADSP shall compare each value inside the OTP memory with the corresponding value in OTP Registers to check if the WRITE routine has been succesfull. In that case ADSP shall write 0xFF into the last location of the OTP memory.</t>
+          <t>During WRITE routine, ADSP shall allow copying all OTP Registers into the OTP Memory only if the location 0x24 of OTP Memory (OTP[24] in the following diagram) is not set to 0xFF. Figure 13: Write Routine Start [Vpriority High]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -11756,7 +11808,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 021 (page 92)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 008 (page 92)</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11776,7 +11828,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0021 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0020 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.91</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11806,12 +11858,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0022</t>
+          <t>DDS_STBIO1_0021</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0022</t>
+          <t>DDS_STBIO1_0021</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -11822,7 +11874,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>OTP_WRITE, OTP_BOOT and OTP_TEST bits shall be cleared by ADSP at the end of their respective operation [Vpriority High]</t>
+          <t>During the WRITE routine and after copying all OTP Registers into the OTP Memory, ADSP shall compare each value inside the OTP memory with the corresponding value in OTP Registers to check if the WRITE routine has been succesfull. In that case ADSP shall write 0xFF into the last location of the OTP memory. Figure 14: WRITE routine and TEST regmap [Vpriority High]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -11832,7 +11884,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 011 (page 93)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 021 (page 92)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11852,7 +11904,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0022 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0021 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.92</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11882,12 +11934,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0023</t>
+          <t>DDS_STBIO1_0022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0023</t>
+          <t>DDS_STBIO1_0022</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -11898,7 +11950,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>A new operation shall start only when quokka_run is low, and one between OTP_TEST bit, OTP_WRITE bit or OTP_BOOT bit is written to 1 [Vpriority High]</t>
+          <t>OTP_WRITE, OTP_BOOT and OTP_TEST bits shall be cleared by ADSP at the end of their respective operation [Vpriority High]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -11908,7 +11960,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 017 (page 93)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 011 (page 93)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11928,7 +11980,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0023 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0022 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11958,12 +12010,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0028</t>
+          <t>DDS_STBIO1_0023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0028</t>
+          <t>DDS_STBIO1_0023</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -11974,7 +12026,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0028] Requirement: The TEST routines shall allow reading an 8-bit word on OTP of a specific address written in OTP_A register, and write this value in OTP_D_TEST register.</t>
+          <t>A new operation shall start only when quokka_run is low, and one between OTP_TEST bit, OTP_WRITE bit or OTP_BOOT bit is written to 1 [Vpriority High]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -11984,7 +12036,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 023 (page 94)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 017 (page 93)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12004,12 +12056,12 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0028 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0023 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -12034,12 +12086,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0024</t>
+          <t>DDS_STBIO1_0028</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0024</t>
+          <t>DDS_STBIO1_0028</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -12050,7 +12102,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>OTP_IREF_WAKEUP shall be set to one by an external I2C/SPI to AHB write before initiating a new OTP_TEST or OTP_WRITE operation [Vpriority High]</t>
+          <t>[DDS_STBIO1_0028] Requirement: The TEST routines shall allow reading an 8-bit word on OTP of a specific address written in OTP_A register, and write this value in OTP_D_TEST register.</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -12060,7 +12112,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 004 (page 94)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 023 (page 94)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -12080,12 +12132,12 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0024 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0028 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -12110,12 +12162,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0025</t>
+          <t>DDS_STBIO1_0024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0025</t>
+          <t>DDS_STBIO1_0024</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -12126,7 +12178,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>OTP_IREF_WAKEUP shall be setted to zero by an external I2C/SPI to AHB write at the end of OTP_TEST or OTP_WRITE operation [Vpriority High]</t>
+          <t>OTP_IREF_WAKEUP shall be set to one by an external I2C/SPI to AHB write before initiating a new OTP_TEST or OTP_WRITE operation [Vpriority High]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -12136,7 +12188,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 009 (page 94)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 004 (page 94)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -12156,7 +12208,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0025 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0024 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12186,12 +12238,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0026</t>
+          <t>DDS_STBIO1_0025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0026</t>
+          <t>DDS_STBIO1_0025</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -12202,17 +12254,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>After startup phase, once started with an operation, the IP shall ignore any further start incoming transactions. [Vpriority High]</t>
+          <t>OTP_IREF_WAKEUP shall be setted to zero by an external I2C/SPI to AHB write at the end of OTP_TEST or OTP_WRITE operation [Vpriority High]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 014 (page 94)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 009 (page 94)</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -12232,7 +12284,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0026 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0025 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12262,12 +12314,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0027</t>
+          <t>DDS_STBIO1_0026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0027</t>
+          <t>DDS_STBIO1_0026</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -12278,17 +12330,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>The TEST routine shall start when OTP Test Bit rises and completes when quokka_run falls. [Vpriority High]</t>
+          <t>After startup phase, once started with an operation, the IP shall ignore any further start incoming transactions. [Vpriority High]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 019 (page 94)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 014 (page 94)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -12308,7 +12360,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0027 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0026 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12338,12 +12390,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0034</t>
+          <t>DDS_STBIO1_0027</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0034</t>
+          <t>DDS_STBIO1_0027</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -12354,17 +12406,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>During the Soft Reset routine, ADSP shall write the ADSP RAM with the value 0. Only the first 3.5Kbyte of ADSP RAM shall be cleared, from address 0x000 to address 0xDFF [Vpriority High]</t>
+          <t>The TEST routine shall start when OTP Test Bit rises and completes when quokka_run falls. [Vpriority High]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 013 (page 97)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 019 (page 94)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12384,7 +12436,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0034 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0027 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12414,12 +12466,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0036</t>
+          <t>DDS_STBIO1_0034</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0036</t>
+          <t>DDS_STBIO1_0034</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -12430,20 +12482,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0036] Requirement: If bit OTP_PRG10[31] in OTP Registers, called write_protection_en, is set to 1, and STBIO1 is not in debug_mode, register map shall refuse any incoming write request if the transaction address is within the OTP Registers space (from 0xCD000 to 0xCD02F).</t>
+          <t>During the Soft Reset routine, ADSP shall write the ADSP RAM with the value 0. Only the first 3.5Kbyte of ADSP RAM shall be cleared, from address 0x000 to address 0xDFF [Vpriority High]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Section 4 OTP BOOT routine, paragraph 030 (page 97)</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 013 (page 97)</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>ADSP</t>
+        </is>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
           <t>raw</t>
@@ -12456,12 +12512,12 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0036 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.97</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0034 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -12480,26 +12536,18 @@
         </is>
       </c>
       <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>within the OTP Registers space (from 0xCD000 to 0xCD02F)</t>
-        </is>
-      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0032</t>
+          <t>DDS_STBIO1_0036</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0032</t>
+          <t>DDS_STBIO1_0036</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -12510,22 +12558,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>After each Boot routine performed by the ADSP, a value of 0x04 shall be written once to address 0x0CA00C to ensure correct operation of the AHB transactions. [Vpriority High]</t>
+          <t>[DDS_STBIO1_0036] Requirement: If bit OTP_PRG10[31] in OTP Registers, called write_protection_en, is set to 1, and STBIO1 is not in debug_mode, register map shall refuse any incoming write request if the transaction address is within the OTP Registers space (from 0xCD000 to 0xCD02F).</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 003 (page 97)</t>
+          <t>Section 4 OTP BOOT routine, paragraph 030 (page 97)</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>ADSP</t>
+          <t>OTP</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12540,12 +12588,12 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0032 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0036 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.97</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -12564,18 +12612,26 @@
         </is>
       </c>
       <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>within the OTP Registers space (from 0xCD000 to 0xCD02F)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0033</t>
+          <t>DDS_STBIO1_0032</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0033</t>
+          <t>DDS_STBIO1_0032</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -12586,17 +12642,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>The Soft Reset routine shall start when SOFT_RESET Bit (in CONTROL_A register) rises and completes when quokka_run falls. [Vpriority High]</t>
+          <t>After each Boot routine performed by the ADSP, a value of 0x04 shall be written once to address 0x0CA00C to ensure correct operation of the AHB transactions. [Vpriority High]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 008 (page 97)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 003 (page 97)</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -12616,7 +12672,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0033 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0032 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12646,12 +12702,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0035</t>
+          <t>DDS_STBIO1_0033</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0035</t>
+          <t>DDS_STBIO1_0033</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -12662,7 +12718,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>If during the start of a new operation, more than one bit is written into CONTROL_A reg in the same write operation, ADSP shall execute only the routine at higher priority and discard the others. Priority is listed below, with first routine at higher priority: 1. SOFT RESET routine 2. OTP WRITE routine 3. OTP TEST routine 4. OTP BOOT routine [Vpriority High]</t>
+          <t>The Soft Reset routine shall start when SOFT_RESET Bit (in CONTROL_A register) rises and completes when quokka_run falls. [Vpriority High]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -12672,7 +12728,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 019 (page 97)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 008 (page 97)</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12692,7 +12748,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0035 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0033 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12722,12 +12778,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8100</t>
+          <t>DDS_STBIO1_0035</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8100</t>
+          <t>DDS_STBIO1_0035</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -12738,7 +12794,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CONNECTION fifo_dpt 8 FIFO depth. Suggested val 8</t>
+          <t>If during the start of a new operation, more than one bit is written into CONTROL_A reg in the same write operation, ADSP shall execute only the routine at higher priority and discard the others. Priority is listed below, with first routine at higher priority: 1. SOFT RESET routine 2. OTP WRITE routine 3. OTP TEST routine 4. OTP BOOT routine [Vpriority High]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -12748,10 +12804,14 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 008 (page 99)</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 019 (page 97)</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>ADSP</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
           <t>raw</t>
@@ -12764,7 +12824,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[4,6,7,8] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8100 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0035 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12794,12 +12854,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8101</t>
+          <t>DDS_STBIO1_8100</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8101</t>
+          <t>DDS_STBIO1_8100</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -12810,17 +12870,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>rd_to_max_val 6000 Time available between double byte write to communicate the number of bytes to be read and the following read. If timer expires the operation is aborted and proper flag is activated. Suggested val. 1200</t>
+          <t>CONNECTION fifo_dpt 8 FIFO depth. Suggested val 8</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 025 (page 99)</t>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 008 (page 99)</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
@@ -12836,7 +12896,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8101 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[4,6,7,8] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8100 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12866,12 +12926,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8102</t>
+          <t>DDS_STBIO1_8101</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8102</t>
+          <t>DDS_STBIO1_8101</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -12882,17 +12942,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>i2c_hs_mode 1'b0 To activate HS I2C</t>
+          <t>rd_to_max_val 6000 Time available between double byte write to communicate the number of bytes to be read and the following read. If timer expires the operation is aborted and proper flag is activated. Suggested val. 1200</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 028 (page 99)</t>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 025 (page 99)</t>
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
@@ -12908,7 +12968,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[26,27,28] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8102 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8101 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12938,12 +12998,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8103</t>
+          <t>DDS_STBIO1_8102</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8103</t>
+          <t>DDS_STBIO1_8102</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -12954,7 +13014,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>i2c_master_code 8'h00 Master code for HS I2C</t>
+          <t>i2c_hs_mode 1'b0 To activate HS I2C</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -12964,7 +13024,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 031 (page 99)</t>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 028 (page 99)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -12980,7 +13040,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[29,30,31] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8103 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[26,27,28] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8102 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -13010,12 +13070,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8104</t>
+          <t>DDS_STBIO1_8103</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8104</t>
+          <t>DDS_STBIO1_8103</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -13026,7 +13086,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ser_mode "i2c_spi" To choose if the interface is SPI only, I2C only or both. Suggested : i2c_spi</t>
+          <t>i2c_master_code 8'h00 Master code for HS I2C</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -13036,7 +13096,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 039 (page 99)</t>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 031 (page 99)</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
@@ -13052,7 +13112,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[32,33,34,35,36,37,38,39] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8104 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[29,30,31] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8103 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13072,7 +13132,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -13082,12 +13142,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8105</t>
+          <t>DDS_STBIO1_8104</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8105</t>
+          <t>DDS_STBIO1_8104</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13098,17 +13158,17 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ip_version 8'haa IP version</t>
+          <t>ser_mode "i2c_spi" To choose if the interface is SPI only, I2C only or both. Suggested : i2c_spi</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 040 (page 99)</t>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 039 (page 99)</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
@@ -13124,7 +13184,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[40] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8105 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[32,33,34,35,36,37,38,39] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8104 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13144,7 +13204,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="P174" t="inlineStr"/>
@@ -13154,12 +13214,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8106</t>
+          <t>DDS_STBIO1_8105</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8106</t>
+          <t>DDS_STBIO1_8105</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13170,17 +13230,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>i2c_dev_id 7'h5f I2C device address</t>
+          <t>ip_version 8'haa IP version</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 041 (page 99)</t>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 040 (page 99)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
@@ -13196,7 +13256,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[41] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8106 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[40] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8105 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13226,12 +13286,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8000</t>
+          <t>DDS_STBIO1_8106</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8000</t>
+          <t>DDS_STBIO1_8106</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13242,7 +13302,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_8000] Requirement: I2C interface shall support all the specified modalities (Standard, FM, FM+) and, if configured, HS is also supported.</t>
+          <t>i2c_dev_id 7'h5f I2C device address</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -13252,14 +13312,10 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 005 (page 102)</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>I2C_SPI_AHB</t>
-        </is>
-      </c>
+          <t>Section 13.2.2 I2C_SPI_AHB integration (under Section 13.2 IPs), paragraph 041 (page 99)</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>raw</t>
@@ -13272,12 +13328,12 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_8000 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page99:lines[41] | recovery_mode=header_split | source_req_id=DDS_STBIO1_8106 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a interface requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -13292,7 +13348,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -13302,12 +13358,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8001</t>
+          <t>DDS_STBIO1_8000</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8001</t>
+          <t>DDS_STBIO1_8000</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13318,7 +13374,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Clock frequency ratio between system (AHB) and I2C/SPI interfaces domains shall be at least 2 times. [TO: IPOS_I2C_SPI_AHB_0006] [Vpriority High]</t>
+          <t>[DDS_STBIO1_8000] Requirement: I2C interface shall support all the specified modalities (Standard, FM, FM+) and, if configured, HS is also supported.</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -13328,7 +13384,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 009 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 005 (page 102)</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13348,12 +13404,12 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8001 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_8000 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a interface requirement.</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -13368,26 +13424,22 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>at least 2 times</t>
-        </is>
-      </c>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8003</t>
+          <t>DDS_STBIO1_8001</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8003</t>
+          <t>DDS_STBIO1_8001</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13398,7 +13450,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>An I2C/SPI write access to the address 0x60-0x67 shall be translated in an AHB write access to the configured AHB address (contained in registers SAM_ADDR_BYTE0/1/2/3, address 0x50/0x51/0x52/0x53). [TO: IPOS_I2C_SPI_AHB_0009] [Vpriority High]</t>
+          <t>Clock frequency ratio between system (AHB) and I2C/SPI interfaces domains shall be at least 2 times. [TO: IPOS_I2C_SPI_AHB_0006] [Vpriority High]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -13408,7 +13460,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 020 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 009 (page 102)</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13428,7 +13480,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8003 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8001 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13453,17 +13505,21 @@
       </c>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>at least 2 times</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8004</t>
+          <t>DDS_STBIO1_8003</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8004</t>
+          <t>DDS_STBIO1_8003</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -13474,7 +13530,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>A double byte write access to the address 0x68-0x6f (with data that is the number of bytes that the master wants to read) shall start the data preload from AHB in order to have the internal fifo not empty when the read request will be done by the master. [TO: IPOS_I2C_SPI_AHB_0010] [Vpriority High]</t>
+          <t>An I2C/SPI write access to the address 0x60-0x67 shall be translated in an AHB write access to the configured AHB address (contained in registers SAM_ADDR_BYTE0/1/2/3, address 0x50/0x51/0x52/0x53). [TO: IPOS_I2C_SPI_AHB_0009] [Vpriority High]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -13484,7 +13540,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 027 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 020 (page 102)</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13504,7 +13560,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8004 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8003 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13534,12 +13590,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8005</t>
+          <t>DDS_STBIO1_8004</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8005</t>
+          <t>DDS_STBIO1_8004</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13550,7 +13606,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>An I2C/SPI read access to the address 0x70-0x7f shall be translated in an AHB read access to the configured AHB address (contained in registers SAM_ADDR_BYTE0/1/2/3, address 0x50/0x51/0x52/0x53). [TO: IPOS_I2C_SPI_AHB_0011] [Vpriority High]</t>
+          <t>A double byte write access to the address 0x68-0x6f (with data that is the number of bytes that the master wants to read) shall start the data preload from AHB in order to have the internal fifo not empty when the read request will be done by the master. [TO: IPOS_I2C_SPI_AHB_0010] [Vpriority High]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -13560,7 +13616,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 035 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 027 (page 102)</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13580,7 +13636,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8005 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8004 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13610,12 +13666,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8002</t>
+          <t>DDS_STBIO1_8005</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8002</t>
+          <t>DDS_STBIO1_8005</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -13626,7 +13682,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>The IP has a serial interface (I2C or SPI) and a parallel bus interface AHB. [TO: IPOS_I2C_SPI_AHB_0007]</t>
+          <t>An I2C/SPI read access to the address 0x70-0x7f shall be translated in an AHB read access to the configured AHB address (contained in registers SAM_ADDR_BYTE0/1/2/3, address 0x50/0x51/0x52/0x53). [TO: IPOS_I2C_SPI_AHB_0011] [Vpriority High]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -13636,7 +13692,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 015 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 035 (page 102)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13656,7 +13712,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8002 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8005 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13676,7 +13732,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P181" t="inlineStr"/>
@@ -13686,12 +13742,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8006</t>
+          <t>DDS_STBIO1_8002</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8006</t>
+          <t>DDS_STBIO1_8002</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -13702,7 +13758,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>On AHB interface, data size shall be limited to BYTE and WORD. [TO: IPOS_I2C_SPI_AHB_0361]</t>
+          <t>The IP has a serial interface (I2C or SPI) and a parallel bus interface AHB. [TO: IPOS_I2C_SPI_AHB_0007]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -13712,7 +13768,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 042 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 015 (page 102)</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13732,7 +13788,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8006 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8002 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13762,12 +13818,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8007</t>
+          <t>DDS_STBIO1_8006</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_8007</t>
+          <t>DDS_STBIO1_8006</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -13778,7 +13834,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>On AHB interface, BURST shall not be supported as well as LOCKED transfers. [TO: IPOS_I2C_SPI_AHB_0362]</t>
+          <t>On AHB interface, data size shall be limited to BYTE and WORD. [TO: IPOS_I2C_SPI_AHB_0361]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -13788,7 +13844,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 047 (page 102)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 042 (page 102)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13808,7 +13864,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8007 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.93</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8006 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13838,12 +13894,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9317</t>
+          <t>DDS_STBIO1_8007</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9317</t>
+          <t>DDS_STBIO1_8007</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -13854,7 +13910,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>If the sensor hub IP is not enabled, the SCL and SDA pad shall not toggle. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>On AHB interface, BURST shall not be supported as well as LOCKED transfers. [TO: IPOS_I2C_SPI_AHB_0362]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -13864,12 +13920,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 017 (page 109)</t>
+          <t>Section 13.2.2.1 I2C_SPI_AHB Peculiar Requirements (under Section 13.2.2 I2C_SPI_AHB integration), paragraph 047 (page 102)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sensor-Hub</t>
+          <t>I2C_SPI_AHB</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13884,7 +13940,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9317 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_8007 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.93</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13904,26 +13960,22 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
+      <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9013</t>
+          <t>DDS_STBIO1_9317</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9013</t>
+          <t>DDS_STBIO1_9317</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -13934,7 +13986,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Output scl_master_out of sensor hub shall be connected to enable of output buffer of sensor hub's SCL PAD in case it is a bi-directional PAD). [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>If the sensor hub IP is not enabled, the SCL and SDA pad shall not toggle. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -13944,7 +13996,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 034 (page 109)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 017 (page 109)</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13964,7 +14016,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9013 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9317 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13988,18 +14040,22 @@
         </is>
       </c>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9014</t>
+          <t>DDS_STBIO1_9013</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9014</t>
+          <t>DDS_STBIO1_9013</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -14010,7 +14066,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Output sda_master_out of sensor hub shall be connected to enable of output buffer of sensor hub's SDA PAD. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>Output scl_master_out of sensor hub shall be connected to enable of output buffer of sensor hub's SCL PAD in case it is a bi-directional PAD). [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -14020,7 +14076,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 040 (page 109)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 034 (page 109)</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -14040,7 +14096,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9014 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9013 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14070,12 +14126,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9011</t>
+          <t>DDS_STBIO1_9014</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9011</t>
+          <t>DDS_STBIO1_9014</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -14086,7 +14142,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Input scl_master_in of sensor hub shall be connected to input buffer from sensor hub's SCL PAD. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>Output sda_master_out of sensor hub shall be connected to enable of output buffer of sensor hub's SDA PAD. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -14096,7 +14152,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 022 (page 109)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 040 (page 109)</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -14116,7 +14172,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9011 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9014 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14146,12 +14202,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9012</t>
+          <t>DDS_STBIO1_9011</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9012</t>
+          <t>DDS_STBIO1_9011</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -14162,7 +14218,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Input sda_master_in of sensor hub shall be connected to input buffer from sensor hub's SDA PAD. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>Input scl_master_in of sensor hub shall be connected to input buffer from sensor hub's SCL PAD. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -14172,7 +14228,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 028 (page 109)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 022 (page 109)</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -14192,7 +14248,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9012 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9011 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14222,12 +14278,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9017</t>
+          <t>DDS_STBIO1_9012</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9017</t>
+          <t>DDS_STBIO1_9012</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -14238,7 +14294,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>The output port sleep_master shall be set to 1 when an I2C operation is not on-going. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>Input sda_master_in of sensor hub shall be connected to input buffer from sensor hub's SDA PAD. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -14248,7 +14304,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 046 (page 109)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 028 (page 109)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14268,7 +14324,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9017 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9012 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14288,7 +14344,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14298,12 +14354,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9004</t>
+          <t>DDS_STBIO1_9017</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9004</t>
+          <t>DDS_STBIO1_9017</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14314,7 +14370,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Input sys_clk of sensor hub shall be connected to 8MHz clock to generate I2C communications compliant with FM+ I2C standard. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>The output port sleep_master shall be set to 1 when an I2C operation is not on-going. [Vpriority High] [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -14324,7 +14380,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 051 (page 109)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 046 (page 109)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14344,7 +14400,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9004 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:partial_overlap=0.74</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9017 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14364,7 +14420,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -14374,12 +14430,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9018</t>
+          <t>DDS_STBIO1_9004</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9018</t>
+          <t>DDS_STBIO1_9004</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14390,7 +14446,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9018] Requirement The trigger of sensor hub shall be possible in both ways, HW via dvalid_masterblaze_ext signal or SW using DVALID_REGISTER.</t>
+          <t>Input sys_clk of sensor hub shall be connected to 8MHz clock to generate I2C communications compliant with FM+ I2C standard. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -14400,7 +14456,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 008 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 051 (page 109)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -14420,12 +14476,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9018 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9004 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:partial_overlap=0.74</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a functional requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -14450,12 +14506,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9024</t>
+          <t>DDS_STBIO1_9018</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9024</t>
+          <t>DDS_STBIO1_9018</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14466,7 +14522,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9024] Requirement Only I2C target addressed through SLAVE0_DEV_ADD register shall be the destination of an I2C Write Operation.</t>
+          <t>[DDS_STBIO1_9018] Requirement The trigger of sensor hub shall be possible in both ways, HW via dvalid_masterblaze_ext signal or SW using DVALID_REGISTER.</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -14476,7 +14532,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 014 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 008 (page 110)</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -14496,12 +14552,12 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9024 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9018 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Narrative sentence states device behavior classified as a functional requirement.</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -14516,7 +14572,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -14526,12 +14582,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9027</t>
+          <t>DDS_STBIO1_9024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9027</t>
+          <t>DDS_STBIO1_9024</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14542,7 +14598,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9027] Requirement The bit 0 of SLAVE1_DEV_ADD, SLAVE2_DEV_ADD, SLAVE3_DEV_ADD registers shall be ignored: ONLY read operations towards I2C target 1, 2 and 3 shall be performed.</t>
+          <t>[DDS_STBIO1_9024] Requirement Only I2C target addressed through SLAVE0_DEV_ADD register shall be the destination of an I2C Write Operation.</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -14552,7 +14608,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 020 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 014 (page 110)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -14572,7 +14628,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9027 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9024 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14602,12 +14658,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9030</t>
+          <t>DDS_STBIO1_9027</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9030</t>
+          <t>DDS_STBIO1_9027</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14618,7 +14674,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9030] Requirement SLAVEx_NUMOP bit-fields of SLAVEx_CONFIG registers shall define how many bytes per slave are read as per effect of an I2C operation (x from 1 to 12).</t>
+          <t>[DDS_STBIO1_9027] Requirement The bit 0 of SLAVE1_DEV_ADD, SLAVE2_DEV_ADD, SLAVE3_DEV_ADD registers shall be ignored: ONLY read operations towards I2C target 1, 2 and 3 shall be performed.</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -14628,7 +14684,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 032 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 020 (page 110)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14648,7 +14704,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9030 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9027 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14678,12 +14734,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9032</t>
+          <t>DDS_STBIO1_9030</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9032</t>
+          <t>DDS_STBIO1_9030</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14694,7 +14750,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9032] Requirement SLAVE0_NUMOP bitfield shall be ignored if an I2C Write operation is issued to the I2C Slave 0.</t>
+          <t>[DDS_STBIO1_9030] Requirement SLAVEx_NUMOP bit-fields of SLAVEx_CONFIG registers shall define how many bytes per slave are read as per effect of an I2C operation (x from 1 to 12).</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -14704,7 +14760,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 044 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 032 (page 110)</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -14724,7 +14780,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9032 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9030 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14754,12 +14810,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9029</t>
+          <t>DDS_STBIO1_9032</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9029</t>
+          <t>DDS_STBIO1_9032</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14770,7 +14826,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AUX_SENS_ON possible values shall be 0,1,2,3. All the values shall be tested since MasterBlaze supports up-to 4 I2C targets connected to I2C network. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>[DDS_STBIO1_9032] Requirement SLAVE0_NUMOP bitfield shall be ignored if an I2C Write operation is issued to the I2C Slave 0.</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -14780,7 +14836,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 026 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 044 (page 110)</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14800,12 +14856,12 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9029 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9032 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -14830,12 +14886,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9031</t>
+          <t>DDS_STBIO1_9029</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9031</t>
+          <t>DDS_STBIO1_9029</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14846,7 +14902,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>All the values from 1 to 12 shall be valid for SLAVEx_NUMOP bit-fields of SLAVEx_CONFIG registers. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>AUX_SENS_ON possible values shall be 0,1,2,3. All the values shall be tested since MasterBlaze supports up-to 4 I2C targets connected to I2C network. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -14856,7 +14912,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 038 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 026 (page 110)</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14876,7 +14932,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9031 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9029 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14906,12 +14962,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9033</t>
+          <t>DDS_STBIO1_9031</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9033</t>
+          <t>DDS_STBIO1_9031</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14922,7 +14978,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>All the SENSOR_HUB_x registers shall be reset every time a new I2C operation starts. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>All the values from 1 to 12 shall be valid for SLAVEx_NUMOP bit-fields of SLAVEx_CONFIG registers. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -14932,7 +14988,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 049 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 038 (page 110)</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14952,7 +15008,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9033 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9031 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14982,12 +15038,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9035</t>
+          <t>DDS_STBIO1_9033</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9035</t>
+          <t>DDS_STBIO1_9033</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14998,7 +15054,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>When Quokka MasterBlaze µP runs (sleep_master signal = 0), any dvalid triggered (HW or SW) shall be ignored. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>All the SENSOR_HUB_x registers shall be reset every time a new I2C operation starts. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -15008,7 +15064,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 054 (page 110)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 049 (page 110)</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15028,7 +15084,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9035 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9033 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -15058,12 +15114,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9300</t>
+          <t>DDS_STBIO1_9035</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9300</t>
+          <t>DDS_STBIO1_9035</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -15074,7 +15130,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9300] Requirement The AHB Write to registers has no effect if the IP masterblaze processor is busy (I2C operation on-going); the registers value shall not be updated.</t>
+          <t>When Quokka MasterBlaze µP runs (sleep_master signal = 0), any dvalid triggered (HW or SW) shall be ignored. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -15084,7 +15140,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 033 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 054 (page 110)</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -15104,12 +15160,12 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9300 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9035 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15134,12 +15190,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9500</t>
+          <t>DDS_STBIO1_9300</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9500</t>
+          <t>DDS_STBIO1_9300</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -15150,7 +15206,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_9500] Requirement In case also other sources that writes into FIFO are active, then sensor hub shall work always in multi-fifo mode fifo_mode input of sensor hub set to '1' .</t>
+          <t>[DDS_STBIO1_9300] Requirement The AHB Write to registers has no effect if the IP masterblaze processor is busy (I2C operation on-going); the registers value shall not be updated.</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15160,7 +15216,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 039 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 033 (page 111)</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -15180,12 +15236,12 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9500 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9300 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a functional requirement.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15200,7 +15256,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P201" t="inlineStr"/>
@@ -15210,12 +15266,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9034</t>
+          <t>DDS_STBIO1_9500</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9034</t>
+          <t>DDS_STBIO1_9500</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -15226,7 +15282,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>The NACK_REGISTER register is reset every time a new I2C operation starts. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>[DDS_STBIO1_9500] Requirement In case also other sources that writes into FIFO are active, then sensor hub shall work always in multi-fifo mode fifo_mode input of sensor hub set to '1' .</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15236,7 +15292,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 008 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 039 (page 111)</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -15256,12 +15312,12 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9034 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_9500 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a functional requirement.</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15276,7 +15332,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P202" t="inlineStr"/>
@@ -15286,12 +15342,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9260</t>
+          <t>DDS_STBIO1_9034</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9260</t>
+          <t>DDS_STBIO1_9034</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -15302,7 +15358,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Each data stored in FIFO shall be composed by 4 words (16bytes). [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>The NACK_REGISTER register is reset every time a new I2C operation starts. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -15312,7 +15368,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 013 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 008 (page 111)</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -15332,7 +15388,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9260 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9034 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15362,12 +15418,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9261</t>
+          <t>DDS_STBIO1_9260</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9261</t>
+          <t>DDS_STBIO1_9260</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15378,7 +15434,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>3 words (12bytes) of the data stored in FIFO shall contain the data from each I2C slave. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>Each data stored in FIFO shall be composed by 4 words (16bytes). [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -15388,7 +15444,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 018 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 013 (page 111)</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -15408,7 +15464,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9261 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9260 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15438,12 +15494,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9262</t>
+          <t>DDS_STBIO1_9261</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9262</t>
+          <t>DDS_STBIO1_9261</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15454,7 +15510,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>24-bits of the data stored in FIFO shall be reserved at '0'. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>3 words (12bytes) of the data stored in FIFO shall contain the data from each I2C slave. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -15464,7 +15520,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 023 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 018 (page 111)</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -15484,7 +15540,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9262 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9261 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15514,12 +15570,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9263</t>
+          <t>DDS_STBIO1_9262</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_9263</t>
+          <t>DDS_STBIO1_9262</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15530,7 +15586,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>The last 8-bits of the data stored in FIFO shall contain the TAG field. [TO: IPOS_Senshub_MB_i2c]</t>
+          <t>24-bits of the data stored in FIFO shall be reserved at '0'. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -15540,7 +15596,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 028 (page 111)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 023 (page 111)</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -15560,7 +15616,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9263 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9262 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15590,12 +15646,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000102</t>
+          <t>DDS_STBIO1_9263</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000102</t>
+          <t>DDS_STBIO1_9263</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15606,7 +15662,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>The parameter MEM_LOC shall define the first Memory Location of the FIFO RAM: 0xC4000. [TO: IPOS_FIFO_CTRL_00000102]</t>
+          <t>The last 8-bits of the data stored in FIFO shall contain the TAG field. [TO: IPOS_Senshub_MB_i2c]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -15616,12 +15672,12 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 004 (page 113)</t>
+          <t>Section 13.2.3.1 SensorHub Peculiar Requirements (under Section 13.2.3 SensorHub integration), paragraph 028 (page 111)</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Smart FIFO</t>
+          <t>Sensor-Hub</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15636,7 +15692,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00000102 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_9263 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15646,7 +15702,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Requirement</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15656,7 +15712,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P207" t="inlineStr"/>
@@ -15666,12 +15722,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000202</t>
+          <t>DDS_STBIO1_00000102</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000202</t>
+          <t>DDS_STBIO1_00000102</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -15682,7 +15738,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>The FIFO register map first memory location shall be defined as MEM_LOC + 0x1000: 0xC5000. [TO: IPOS_FIFO_CTRL_00000202]</t>
+          <t>The parameter MEM_LOC shall define the first Memory Location of the FIFO RAM: 0xC4000. [TO: IPOS_FIFO_CTRL_00000102]</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -15692,7 +15748,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 009 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 004 (page 113)</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -15712,7 +15768,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00000202 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00000102 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15722,7 +15778,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Requirement</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15732,7 +15788,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>configuration</t>
         </is>
       </c>
       <c r="P208" t="inlineStr"/>
@@ -15742,12 +15798,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89456557</t>
+          <t>DDS_STBIO1_00000202</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89456557</t>
+          <t>DDS_STBIO1_00000202</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -15758,7 +15814,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>The FIFO Controller shall be able to address 1.5 kbyte divided into 32-bit address. [TO: IPOS_FIFO_CTRL_89456557]</t>
+          <t>The FIFO register map first memory location shall be defined as MEM_LOC + 0x1000: 0xC5000. [TO: IPOS_FIFO_CTRL_00000202]</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -15768,7 +15824,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 014 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 009 (page 113)</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -15788,7 +15844,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89456557 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00000202 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15818,12 +15874,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89459082</t>
+          <t>DDS_STBIO1_89456557</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89459082</t>
+          <t>DDS_STBIO1_89456557</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15834,7 +15890,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>The FIFO Controller shall work at 16 MHz clock frequency. [TO: IPOS_FIFO_CTRL_89459082]</t>
+          <t>The FIFO Controller shall be able to address 1.5 kbyte divided into 32-bit address. [TO: IPOS_FIFO_CTRL_89456557]</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -15844,7 +15900,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 018 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 014 (page 113)</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -15864,7 +15920,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89459082 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89456557 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15894,12 +15950,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89455261</t>
+          <t>DDS_STBIO1_89459082</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89455261</t>
+          <t>DDS_STBIO1_89459082</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15910,7 +15966,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>The FIFO Controller shall have an AHB Slave Interface connected to the AHB BUS and a Memory Master Interface connected to the Physical Memory. [TO: IPOS_FIFO_CTRL_89455261]</t>
+          <t>The FIFO Controller shall work at 16 MHz clock frequency. [TO: IPOS_FIFO_CTRL_89459082]</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -15920,7 +15976,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 022 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 018 (page 113)</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -15940,7 +15996,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89455261 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89459082 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15960,7 +16016,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P211" t="inlineStr"/>
@@ -15970,12 +16026,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89455449</t>
+          <t>DDS_STBIO1_89455261</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89455449</t>
+          <t>DDS_STBIO1_89455261</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15986,7 +16042,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>The FIFO Controller shall have two working modes: Multiple FIFO and Unique FIFO. These two modes are mutually exclusive. [TO: IPOS_FIFO_CTRL_89455449]</t>
+          <t>The FIFO Controller shall have an AHB Slave Interface connected to the AHB BUS and a Memory Master Interface connected to the Physical Memory. [TO: IPOS_FIFO_CTRL_89455261]</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -15996,7 +16052,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 027 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 022 (page 113)</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -16016,7 +16072,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89455449 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89455261 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -16036,7 +16092,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="P212" t="inlineStr"/>
@@ -16046,12 +16102,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89455232</t>
+          <t>DDS_STBIO1_89455449</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89455232</t>
+          <t>DDS_STBIO1_89455449</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -16062,7 +16118,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>As default, the FIFO shall work in Unique FIFO Mode. [TO: IPOS_FIFO_CTRL_89455232]</t>
+          <t>The FIFO Controller shall have two working modes: Multiple FIFO and Unique FIFO. These two modes are mutually exclusive. [TO: IPOS_FIFO_CTRL_89455449]</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -16072,7 +16128,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 032 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 027 (page 113)</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -16092,7 +16148,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89455232 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89455449 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16122,12 +16178,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89456975</t>
+          <t>DDS_STBIO1_89455232</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89456975</t>
+          <t>DDS_STBIO1_89455232</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -16138,7 +16194,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>The user shall select the Multiple FIFO mode setting to 1 the first bit into the FIFO_CFG_MODE and 0 for the Unique FIFO mode. [TO: IPOS_FIFO_CTRL_89456975]</t>
+          <t>As default, the FIFO shall work in Unique FIFO Mode. [TO: IPOS_FIFO_CTRL_89455232]</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -16148,7 +16204,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 036 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 032 (page 113)</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -16168,7 +16224,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89456975 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89455232 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16198,12 +16254,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89457435</t>
+          <t>DDS_STBIO1_89456975</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89457435</t>
+          <t>DDS_STBIO1_89456975</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -16214,7 +16270,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>The FIFO Controller shall have a 6 i_depth input of 8 bit to be used in Multiple FIFO Mode to define the depth of each subFIFOs. [TO: IPOS_FIFO_CTRL_89457435]</t>
+          <t>The user shall select the Multiple FIFO mode setting to 1 the first bit into the FIFO_CFG_MODE and 0 for the Unique FIFO mode. [TO: IPOS_FIFO_CTRL_89456975]</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -16224,7 +16280,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 041 (page 113)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 036 (page 113)</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -16244,7 +16300,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89457435 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89456975 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16274,12 +16330,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89457790</t>
+          <t>DDS_STBIO1_89457435</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_89457790</t>
+          <t>DDS_STBIO1_89457435</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -16290,7 +16346,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>The FIFO 6 memory locations to access each sub-FIFO in Multiple mode are obtained adding multiples of 256 to the memory base address. Example: FIFO Memory Base Address = 0xC4000, then: FIFO 0 memory location 0xC4000 FIFO 1 memory location 0xC4100 FIFO 2 memory location 0xC4200 FIFO 3 memory location 0xC4300 FIFO 4 memory location 0xC4400 FIFO 5 memory location 0xC4500 Table 29: SUB FIFO Memory Address [TO: IPOS_FIFO_CTRL_89457790]</t>
+          <t>The FIFO Controller shall have a 6 i_depth input of 8 bit to be used in Multiple FIFO Mode to define the depth of each subFIFOs. [TO: IPOS_FIFO_CTRL_89457435]</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -16300,7 +16356,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 004 (page 114)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 041 (page 113)</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -16320,7 +16376,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89457790 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.90</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89457435 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16350,12 +16406,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000008</t>
+          <t>DDS_STBIO1_89457790</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000008</t>
+          <t>DDS_STBIO1_89457790</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -16366,7 +16422,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>If input signal HMASTER is set to 0 or 1, the FIFO Controller shall enter Memory mode. [TO: IPOS_FIFO_CTRL_00000008]</t>
+          <t>The FIFO 6 memory locations to access each sub-FIFO in Multiple mode are obtained adding multiples of 256 to the memory base address. Example: FIFO Memory Base Address = 0xC4000, then: FIFO 0 memory location 0xC4000 FIFO 1 memory location 0xC4100 FIFO 2 memory location 0xC4200 FIFO 3 memory location 0xC4300 FIFO 4 memory location 0xC4400 FIFO 5 memory location 0xC4500 Table 29: SUB FIFO Memory Address [TO: IPOS_FIFO_CTRL_89457790]</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -16376,7 +16432,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 017 (page 114)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 004 (page 114)</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -16396,7 +16452,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00000008 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_89457790 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.90</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16426,12 +16482,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000199</t>
+          <t>DDS_STBIO1_00000008</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00000199</t>
+          <t>DDS_STBIO1_00000008</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -16452,7 +16508,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 020 (page 114)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 017 (page 114)</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -16472,7 +16528,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page114:lines[18,19,20] | recovery_mode=header_split | source_req_id=DDS_STBIO1_00000199 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00000008 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16502,12 +16558,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00001199</t>
+          <t>DDS_STBIO1_00000199</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_00001199</t>
+          <t>DDS_STBIO1_00000199</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -16518,7 +16574,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>When in Multiple Fifo, the 6 sub-FIFO offset shall coincide with the following table : FIFO OFFSET DATA TYPE ECG FIFO OFFSET ECG0_AC, ECG0_DC BIA FIFO OFFSET BIA_AC_P, BIA_DC_P, BIA_AC_Q, BIA_DC_Q, ECG1_AC, ECG2_DC GSR FIFO OFFSET GSR, ECG1_DC, ECG2_AC PPG FIFO OFFSET PPG Table 31 : FIFO Offset Data Table</t>
+          <t>If input signal HMASTER is set to 0 or 1, the FIFO Controller shall enter Memory mode. [TO: IPOS_FIFO_CTRL_00000008]</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -16528,7 +16584,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 009 (page 115)</t>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 020 (page 114)</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -16548,7 +16604,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00001199 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.97</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page114:lines[18,19,20] | recovery_mode=header_split | source_req_id=DDS_STBIO1_00000199 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16578,19 +16634,15 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0501</t>
+          <t>DDS_STBIO1_00001199</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0501</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>DDS_STBIO1_0501</t>
-        </is>
-      </c>
+          <t>DDS_STBIO1_00001199</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>tagged_preserve</t>
@@ -16598,7 +16650,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>The irq_FIFO_U_M_IRQ_STsATUS interrupt shall be connected to FIFO status to bit 29.</t>
+          <t>When in Multiple Fifo, the 6 sub-FIFO offset shall coincide with the following table : FIFO OFFSET DATA TYPE ECG FIFO OFFSET ECG0_AC, ECG0_DC BIA FIFO OFFSET BIA_AC_P, BIA_DC_P, BIA_AC_Q, BIA_DC_Q, ECG1_AC, ECG2_DC GSR FIFO OFFSET GSR, ECG1_DC, ECG2_AC PPG FIFO OFFSET PPG Table 31 : FIFO Offset Data Table</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -16608,23 +16660,27 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 007 (page 130)</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
+          <t>Section 13.2.4.1 FIFO_CTRL Peculiar Requirements (under Section 13.2.4 FIFO_CTRL integration), paragraph 009 (page 115)</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Smart FIFO</t>
+        </is>
+      </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>interrupt_table_connection</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>derived-from-structure</t>
+          <t>explicit</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[7-7] | source_req_id=DDS_STBIO1_0501 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_00001199 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.97</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16654,17 +16710,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0502</t>
+          <t>DDS_STBIO1_0501</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0502</t>
+          <t>DDS_STBIO1_0501</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0502</t>
+          <t>DDS_STBIO1_0501</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -16674,7 +16730,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>The irq_SENSHUB_STS interrupt shall be connected to SENSOR HUB status to bit 28.</t>
+          <t>The irq_FIFO_U_M_IRQ_STsATUS interrupt shall be connected to FIFO status to bit 29.</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -16684,7 +16740,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 008 (page 130)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 007 (page 130)</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
@@ -16700,7 +16756,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[8-8] | source_req_id=DDS_STBIO1_0502 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
+          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[7-7] | source_req_id=DDS_STBIO1_0501 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16720,7 +16776,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P221" t="inlineStr"/>
@@ -16730,17 +16786,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0503</t>
+          <t>DDS_STBIO1_0502</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0503</t>
+          <t>DDS_STBIO1_0502</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0503</t>
+          <t>DDS_STBIO1_0502</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -16750,7 +16806,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>The irq_ISPU_MC_INTR_STS interrupt shall be connected to ECG, BIA or PPG samples ready for elaboration to bit 27.</t>
+          <t>The irq_SENSHUB_STS interrupt shall be connected to SENSOR HUB status to bit 28.</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -16760,7 +16816,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 009 (page 130)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 008 (page 130)</t>
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
@@ -16776,7 +16832,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[9-10] | source_req_id=DDS_STBIO1_0503 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
+          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[8-8] | source_req_id=DDS_STBIO1_0502 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16796,7 +16852,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P222" t="inlineStr"/>
@@ -16806,17 +16862,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0504</t>
+          <t>DDS_STBIO1_0503</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0504</t>
+          <t>DDS_STBIO1_0503</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0504</t>
+          <t>DDS_STBIO1_0503</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -16826,7 +16882,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>The sw_interrupt interrupt shall be connected to sw interrupt used by ADSP or external user to bit 26:11 16.</t>
+          <t>The irq_ISPU_MC_INTR_STS interrupt shall be connected to ECG, BIA or PPG samples ready for elaboration to bit 27.</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -16836,7 +16892,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 011 (page 130)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 009 (page 130)</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
@@ -16852,7 +16908,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[11-12] | source_req_id=DDS_STBIO1_0504 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
+          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[9-10] | source_req_id=DDS_STBIO1_0503 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16882,17 +16938,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0505</t>
+          <t>DDS_STBIO1_0504</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0505</t>
+          <t>DDS_STBIO1_0504</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0505</t>
+          <t>DDS_STBIO1_0504</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -16902,7 +16958,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>The irq_timer interrupt shall be connected to Internal timer to bit 1.</t>
+          <t>The sw_interrupt interrupt shall be connected to sw interrupt used by ADSP or external user to bit 26:11 16.</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -16912,7 +16968,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 013 (page 130)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 011 (page 130)</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
@@ -16928,7 +16984,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[13-13] | source_req_id=DDS_STBIO1_0505 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
+          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[11-12] | source_req_id=DDS_STBIO1_0504 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16958,15 +17014,19 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0509</t>
+          <t>DDS_STBIO1_0505</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0509</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
+          <t>DDS_STBIO1_0505</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0505</t>
+        </is>
+      </c>
       <c r="D225" t="inlineStr">
         <is>
           <t>tagged_preserve</t>
@@ -16974,38 +17034,38 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0509] Requirement: To put the ISPU into sleep mode, it is necessary to perform a read at address 0x80054.</t>
+          <t>The irq_timer interrupt shall be connected to Internal timer to bit 1.</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 023 (page 131)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 013 (page 130)</t>
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>interrupt_table_connection</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>explicit</t>
+          <t>derived-from-structure</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0509 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Derived from interrupt table columns Interrupt, bit, Description | table_line_info=page130:lines[13-13] | source_req_id=DDS_STBIO1_0505 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:structural_table_derivation</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -17030,12 +17090,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_05010</t>
+          <t>DDS_STBIO1_0509</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_05010</t>
+          <t>DDS_STBIO1_0509</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -17046,7 +17106,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_05010] Requirement: To wake up the ISPU, it is necessary to trigger an interrupt.</t>
+          <t>[DDS_STBIO1_0509] Requirement: To put the ISPU into sleep mode, it is necessary to perform a read at address 0x80054.</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -17056,7 +17116,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 027 (page 131)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 023 (page 131)</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
@@ -17072,7 +17132,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_05010 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0509 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17102,12 +17162,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_05011</t>
+          <t>DDS_STBIO1_05010</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_05011</t>
+          <t>DDS_STBIO1_05010</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -17118,7 +17178,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_05011] Requirement: When the ISPU is in sleep mode, it is possible to perform reads and writes from the data and code memory by triggering an AHB transition.</t>
+          <t>[DDS_STBIO1_05010] Requirement: To wake up the ISPU, it is necessary to trigger an interrupt.</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -17128,7 +17188,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 031 (page 131)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 027 (page 131)</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
@@ -17144,7 +17204,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_05011 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_05010 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17174,12 +17234,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0508</t>
+          <t>DDS_STBIO1_05011</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0508</t>
+          <t>DDS_STBIO1_05011</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -17190,17 +17250,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>To turn off the ISPU shall be: • Disable the power island by writing to regmap POWER CONFIGURATION REGISTER via AHB interface (ADDRESS=0xCA000, DATA=0x00)</t>
+          <t>[DDS_STBIO1_05011] Requirement: When the ISPU is in sleep mode, it is possible to perform reads and writes from the data and code memory by triggering an AHB transition.</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 017 (page 131)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 031 (page 131)</t>
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
@@ -17216,12 +17276,12 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0508 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_05011 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -17236,7 +17296,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P228" t="inlineStr"/>
@@ -17246,12 +17306,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0507</t>
+          <t>DDS_STBIO1_0508</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0507</t>
+          <t>DDS_STBIO1_0508</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -17262,7 +17322,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>After the initial boot phase, to turn on the ISPU shall be: • Select page 3 of the regmap (ADDRESS=0x04, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable user mode by writing to regmap (ADDRESS=0x5E, DATA=0x01) • Enable the power island by writing to regmap POWER CONFIGURATION REGISTER via AHB interface (ADDRESS=0xCA000, DATA=0x01)</t>
+          <t>To turn off the ISPU shall be: • Disable the power island by writing to regmap POWER CONFIGURATION REGISTER via AHB interface (ADDRESS=0xCA000, DATA=0x00)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -17272,7 +17332,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 004 (page 131)</t>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 017 (page 131)</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
@@ -17288,7 +17348,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0507 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0508 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17318,12 +17378,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3000</t>
+          <t>DDS_STBIO1_0507</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3000</t>
+          <t>DDS_STBIO1_0507</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -17334,7 +17394,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>132 **Update-IR** Run-Test/Idle Select-DR-Scan 13.4. STBIO1 Register Map 13.4.1. STBIO1 Register Map Here is described the list of registers in the register map. The AFE_BLOCK registers are accessible by I2C/SPI direct access and AHB interface, while the others are only by AHB. The I2C/SPI direct access mode is done by the HOST INTF port (I2C/SPI AHB) and the address of the AFE_BLOCK registers are arranged in 4 pages of 64 registers. BASE START ADDRESS ADDRESS BLOCK REGISTER WIDTH BASE END ADDRE VREF_TRIM SS RESET REQ_ID 0xC8000 AFE_BLOCK 8 0xC80EB tst_main_reset_n, regmap_sw_resetn</t>
+          <t>After the initial boot phase, to turn on the ISPU shall be: • Select page 3 of the regmap (ADDRESS=0x04, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable user mode by writing to regmap (ADDRESS=0x5E, DATA=0x01) • Enable the power island by writing to regmap POWER CONFIGURATION REGISTER via AHB interface (ADDRESS=0xCA000, DATA=0x01)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -17344,14 +17404,10 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 028 (page 133)</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Regmap</t>
-        </is>
-      </c>
+          <t>Section 13.3.1 Requirements (under Section 13.3 ISPU integration), paragraph 004 (page 131)</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>raw</t>
@@ -17364,7 +17420,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[1,3,6,8,9,10,11,12,15,16,17,18,19,20,21,22,23,24,25,26,28] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3000 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0507 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17384,7 +17440,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>mode-behavior</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="P230" t="inlineStr"/>
@@ -17394,12 +17450,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3001</t>
+          <t>DDS_STBIO1_3000</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3001</t>
+          <t>DDS_STBIO1_3000</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -17410,17 +17466,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>0xC80EC RESERVED 0xC8FFF tst_main_reset_n, regmap_sw_resetn</t>
+          <t>132 **Update-IR** Run-Test/Idle Select-DR-Scan 13.4. STBIO1 Register Map 13.4.1. STBIO1 Register Map Here is described the list of registers in the register map. The AFE_BLOCK registers are accessible by I2C/SPI direct access and AHB interface, while the others are only by AHB. The I2C/SPI direct access mode is done by the HOST INTF port (I2C/SPI AHB) and the address of the AFE_BLOCK registers are arranged in 4 pages of 64 registers. BASE START ADDRESS ADDRESS BLOCK REGISTER WIDTH BASE END ADDRE VREF_TRIM SS RESET REQ_ID 0xC8000 AFE_BLOCK 8 0xC80EB tst_main_reset_n, regmap_sw_resetn</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 033 (page 133)</t>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 028 (page 133)</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -17440,7 +17496,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[29,30,31,33] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3001 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[1,3,6,8,9,10,11,12,15,16,17,18,19,20,21,22,23,24,25,26,28] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3000 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17460,7 +17516,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>mode-behavior</t>
         </is>
       </c>
       <c r="P231" t="inlineStr"/>
@@ -17470,12 +17526,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3002</t>
+          <t>DDS_STBIO1_3001</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3002</t>
+          <t>DDS_STBIO1_3001</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -17486,17 +17542,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>0xC9000 OTP REGISTER 8 0xC902C tst_main_reset_n</t>
+          <t>0xC80EC RESERVED 0xC8FFF tst_main_reset_n, regmap_sw_resetn</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 034 (page 133)</t>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 033 (page 133)</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -17516,7 +17572,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[34] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3002 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[29,30,31,33] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3001 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17546,12 +17602,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3003</t>
+          <t>DDS_STBIO1_3002</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3003</t>
+          <t>DDS_STBIO1_3002</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -17562,17 +17618,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>0xC9030 RESERVED 0xC9FFF tst_main_reset_n, regmap_sw_resetn</t>
+          <t>0xC9000 OTP REGISTER 8 0xC902C tst_main_reset_n</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 039 (page 133)</t>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 034 (page 133)</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -17592,7 +17648,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[35,36,37,39] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3003 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[34] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3002 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17622,12 +17678,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3004</t>
+          <t>DDS_STBIO1_3003</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3004</t>
+          <t>DDS_STBIO1_3003</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -17638,17 +17694,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>0xCA000 SYSTEM_REGISTER 32 0xCA140 tst_main_reset_n, regmap_sw_resetn</t>
+          <t>0xC9030 RESERVED 0xC9FFF tst_main_reset_n, regmap_sw_resetn</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 044 (page 133)</t>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 039 (page 133)</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -17668,7 +17724,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[40,41,42,44] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3004 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[35,36,37,39] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3003 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17698,12 +17754,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3005</t>
+          <t>DDS_STBIO1_3004</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3005</t>
+          <t>DDS_STBIO1_3004</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -17714,17 +17770,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>0xCA144 RESERVED 0xCCFFF tst_main_reset_n, regmap_sw_resetn</t>
+          <t>0xCA000 SYSTEM_REGISTER 32 0xCA140 tst_main_reset_n, regmap_sw_resetn</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 049 (page 133)</t>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 044 (page 133)</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -17744,7 +17800,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[45,46,47,49] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3005 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[40,41,42,44] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3004 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17774,12 +17830,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3006</t>
+          <t>DDS_STBIO1_3005</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_3006</t>
+          <t>DDS_STBIO1_3005</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -17790,17 +17846,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>0xCD000 OTP (TRIMM REGS) 32 0xCD02F tst_main_reset_n, regmap_sw_resetn</t>
+          <t>0xCA144 RESERVED 0xCCFFF tst_main_reset_n, regmap_sw_resetn</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 054 (page 133)</t>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 049 (page 133)</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -17820,7 +17876,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[50,51,52,54] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3006 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[45,46,47,49] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3005 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17850,12 +17906,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_1114</t>
+          <t>DDS_STBIO1_3006</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_1114</t>
+          <t>DDS_STBIO1_3006</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -17866,7 +17922,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>To perform a SOFT Reset procedure, the user shall perform the following steps: 1. If Mode Operation has been set to 1, shall be reset to 0 2. Set the Soft Reset Main Controller Bit (SW_RESETN_REG[0]) to 0 for at least 1 ms 3. Set the Soft Reset Main Controller Bit (SW_RESETN_REG[0]) to 1 4. Wait for the DEVICE_STATUS_REGISTER to reach the IDLE Value</t>
+          <t>0xCD000 OTP (TRIMM REGS) 32 0xCD02F tst_main_reset_n, regmap_sw_resetn</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -17876,10 +17932,14 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Section 14.1 Main Controller Soft Reset (under Section 14 Soft Reset Procedures), paragraph 009 (page 144)</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Section 13.4.1 STBIO1 Register Map (under Section 13.4 STBIO1 Register Map), paragraph 054 (page 133)</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Regmap</t>
+        </is>
+      </c>
       <c r="I237" t="inlineStr">
         <is>
           <t>raw</t>
@@ -17892,7 +17952,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_1114 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR explicit req-id row sweep | table_line_info=page133:lines[50,51,52,54] | recovery_mode=header_split | source_req_id=DDS_STBIO1_3006 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17912,26 +17972,22 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>mode-behavior</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
-      <c r="R237" t="inlineStr">
-        <is>
-          <t>1 ms; at least 1 ms 3</t>
-        </is>
-      </c>
+      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0114</t>
+          <t>DDS_STBIO1_1114</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0114</t>
+          <t>DDS_STBIO1_1114</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -17942,17 +17998,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>At the release of the POR signal from the analog domain, the PMU shall manage the turn-on of the LDO1V8 and starts clocks Start-Up Sequence (reported in PMU IPOS) [TO: IPOS_PMU]</t>
+          <t>To perform a SOFT Reset procedure, the user shall perform the following steps: 1. If Mode Operation has been set to 1, shall be reset to 0</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Section 15.1 BOOT Phase (under Section 15 Measurement Cycle Examples), paragraph 005 (page 145)</t>
+          <t>Section 14.1 Main Controller Soft Reset (under Section 14 Soft Reset Procedures), paragraph 009 (page 144)</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
@@ -17968,7 +18024,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0114 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_1114 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17998,12 +18054,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0115</t>
+          <t>DDS_STBIO1_0114</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0115</t>
+          <t>DDS_STBIO1_0114</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -18014,7 +18070,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>After At least 2 ms from the Release of the POR, the reset of the digital domain shall be de- asserted (an overlook on this part is described in the PMU IPOS) and the device shall start the Boot Phase [TO: IPOS_PMU]</t>
+          <t>At the release of the POR signal from the analog domain, the PMU shall manage the turn-on of the LDO1V8 and starts clocks Start-Up Sequence (reported in PMU IPOS) [TO: IPOS_PMU]</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -18024,7 +18080,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Section 15.1 BOOT Phase (under Section 15 Measurement Cycle Examples), paragraph 009 (page 145)</t>
+          <t>Section 15.1 BOOT Phase (under Section 15 Measurement Cycle Examples), paragraph 005 (page 145)</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
@@ -18040,7 +18096,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0115 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0114 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -18060,26 +18116,22 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr">
-        <is>
-          <t>2 ms; At least 2 ms from the Release of the POR</t>
-        </is>
-      </c>
+      <c r="R239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0116</t>
+          <t>DDS_STBIO1_0115</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0116</t>
+          <t>DDS_STBIO1_0115</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -18090,7 +18142,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>To check the end of the BOOT phase, the user shall read the main_controller_status_register (DEVICE_STATUS_REG register [2:0]) and follow these steps: • Read the DEVICE_STATUS_REG [2:0] • Check if the Value is 1 (BOOT phase still in process) • If the value is 2, then the BOOT phase is ended and the device is in IDLE. [TO: IPOS_MAIN_CTRL]</t>
+          <t>After At least 2 ms from the Release of the POR, the reset of the digital domain shall be de- asserted (an overlook on this part is described in the PMU IPOS) and the device shall start the Boot Phase [TO: IPOS_PMU]</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -18100,7 +18152,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Section 15.1 BOOT Phase (under Section 15 Measurement Cycle Examples), paragraph 013 (page 145)</t>
+          <t>Section 15.1 BOOT Phase (under Section 15 Measurement Cycle Examples), paragraph 009 (page 145)</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -18116,7 +18168,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0116 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0115 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18136,22 +18188,26 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>mode-behavior</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>2 ms; At least 2 ms from the Release of the POR</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0117</t>
+          <t>DDS_STBIO1_0116</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0117</t>
+          <t>DDS_STBIO1_0116</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -18162,7 +18218,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>During the Configuration Phase (IDLE STATE of the Device_FSM), the user shall be able to: • Configure Bio-Channel or Optical Channel, the ADC Calibration and then Start a measurement cycle. • Put the device in Debug-Mode. [TO: IPOS_MAIN_CTRL]</t>
+          <t>To check the end of the BOOT phase, the user shall read the main_controller_status_register (DEVICE_STATUS_REG register [2:0]) and follow these steps: • Read the DEVICE_STATUS_REG [2:0] • Check if the Value is 1 (BOOT phase still in process) • If the value is 2, then the BOOT phase is ended and the device is in IDLE. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -18172,7 +18228,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Section 15.2 Configuration Phase (under Section 15 Measurement Cycle Examples), paragraph 007 (page 146)</t>
+          <t>Section 15.1 BOOT Phase (under Section 15 Measurement Cycle Examples), paragraph 013 (page 145)</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
@@ -18188,7 +18244,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0117 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0116 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18211,23 +18267,19 @@
           <t>mode-behavior</t>
         </is>
       </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>idle state</t>
-        </is>
-      </c>
+      <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0118</t>
+          <t>DDS_STBIO1_0117</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0118</t>
+          <t>DDS_STBIO1_0117</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -18238,7 +18290,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>• The user shall configure time slot duration in DEVICE_CONFIG_OPERATION register [4:2] [TO: IPOS_MAIN_CTRL]</t>
+          <t>During the Configuration Phase (IDLE STATE of the Device_FSM), the user shall be able to: • Configure Bio-Channel or Optical Channel, the ADC Calibration and then Start a measurement cycle. • Put the device in Debug-Mode. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -18248,7 +18300,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Section 1 TIME SLOT LENGTH: (under Section 15.3.1 ECG Only), paragraph 008 (page 148)</t>
+          <t>Section 15.2 Configuration Phase (under Section 15 Measurement Cycle Examples), paragraph 007 (page 146)</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
@@ -18264,7 +18316,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0118 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0117 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18284,22 +18336,26 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="P242" t="inlineStr"/>
+          <t>mode-behavior</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>idle state</t>
+        </is>
+      </c>
       <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0119</t>
+          <t>DDS_STBIO1_0118</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0119</t>
+          <t>DDS_STBIO1_0118</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -18310,7 +18366,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>• The user shall select active channel, in this case only ECG0_SEL and DS_SEL (Data Storage Mode) in DEVICE_CONFIG_CHANNEL register writing 0x21. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall configure time slot duration in DEVICE_CONFIG_OPERATION register [4:2] [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -18320,7 +18376,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Section 2 SELECT CHANNEL: (under Section 15.3.1 ECG Only), paragraph 012 (page 148)</t>
+          <t>Section 1 TIME SLOT LENGTH: (under Section 15.3.1 ECG Only), paragraph 008 (page 148)</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
@@ -18336,7 +18392,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0119 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0118 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18356,7 +18412,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="P243" t="inlineStr"/>
@@ -18366,12 +18422,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0120</t>
+          <t>DDS_STBIO1_0119</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0120</t>
+          <t>DDS_STBIO1_0119</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -18382,7 +18438,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>• The user shall select a division index for ECG, configuring M_ECG_l and M_ECG_h in SET_ECG_FREQ_l register and SET_ECG_FREQ_h register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall select active channel, in this case only ECG0_SEL and DS_SEL (Data Storage Mode) in DEVICE_CONFIG_CHANNEL register writing 0x21. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -18392,7 +18448,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.1 ECG Only), paragraph 017 (page 148)</t>
+          <t>Section 2 SELECT CHANNEL: (under Section 15.3.1 ECG Only), paragraph 012 (page 148)</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
@@ -18408,7 +18464,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0120 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0119 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18438,12 +18494,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0121</t>
+          <t>DDS_STBIO1_0120</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0121</t>
+          <t>DDS_STBIO1_0120</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -18454,7 +18510,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>• The user shall set the number of clocks for sampling ECG data from ADC in ADC_CONFIG_ECG register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall select a division index for ECG, configuring M_ECG_l and M_ECG_h in SET_ECG_FREQ_l register and SET_ECG_FREQ_h register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -18464,7 +18520,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Section 4 CONFIGURE ADC SAMPLING PERIOD: (under Section 15.3.1 ECG Only), paragraph 022 (page 148)</t>
+          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.1 ECG Only), paragraph 017 (page 148)</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
@@ -18480,7 +18536,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0121 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0120 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18500,7 +18556,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P245" t="inlineStr"/>
@@ -18510,12 +18566,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0122</t>
+          <t>DDS_STBIO1_0121</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0122</t>
+          <t>DDS_STBIO1_0121</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -18526,7 +18582,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>• The User shall set at 1 HC_EN in ECG_CTRL register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall set the number of clocks for sampling ECG data from ADC in ADC_CONFIG_ECG register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -18536,7 +18592,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Section 5 GENERAL CONFIG: (under Section 15.3.1 ECG Only), paragraph 027 (page 148)</t>
+          <t>Section 4 CONFIGURE ADC SAMPLING PERIOD: (under Section 15.3.1 ECG Only), paragraph 022 (page 148)</t>
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
@@ -18552,7 +18608,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0122 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0121 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18572,7 +18628,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P246" t="inlineStr"/>
@@ -18582,12 +18638,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0123</t>
+          <t>DDS_STBIO1_0122</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0123</t>
+          <t>DDS_STBIO1_0122</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -18598,7 +18654,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>• The user shall start measurement writing register DEVICE_CONFIG_OPERATION [0] at 1. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The User shall set at 1 HC_EN in ECG_CTRL register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -18608,7 +18664,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Section 6 SELECT OPERATIVE MODE: (under Section 15.3.1 ECG Only), paragraph 031 (page 148)</t>
+          <t>Section 5 GENERAL CONFIG: (under Section 15.3.1 ECG Only), paragraph 027 (page 148)</t>
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
@@ -18624,7 +18680,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0123 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0122 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18644,7 +18700,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P247" t="inlineStr"/>
@@ -18654,12 +18710,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0124</t>
+          <t>DDS_STBIO1_0123</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0124</t>
+          <t>DDS_STBIO1_0123</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -18670,7 +18726,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>• To check data in unique FIFO (default config) the user shall check the first MSB which will have to be equal to the table in DATA TAG Table. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall start measurement writing register DEVICE_CONFIG_OPERATION [0] at 1. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -18680,7 +18736,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Section 7 CHECK DATA: (under Section 15.3.1 ECG Only), paragraph 036 (page 148)</t>
+          <t>Section 6 SELECT OPERATIVE MODE: (under Section 15.3.1 ECG Only), paragraph 031 (page 148)</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -18696,7 +18752,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0124 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0123 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18716,7 +18772,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P248" t="inlineStr"/>
@@ -18726,12 +18782,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0125</t>
+          <t>DDS_STBIO1_0124</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0125</t>
+          <t>DDS_STBIO1_0124</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -18742,7 +18798,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0125] Requirement: • The user shall configure the time slot duration in DEVICE_CONFIG_OPERATION register [4:2].</t>
+          <t>• To check data in unique FIFO (default config) the user shall check the first MSB which will have to be equal to the table in DATA TAG Table. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -18752,7 +18808,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Section 1 TIME SLOT LENGTH: (under Section 15.3.2 ECG and BIA), paragraph 012 (page 150)</t>
+          <t>Section 7 CHECK DATA: (under Section 15.3.1 ECG Only), paragraph 036 (page 148)</t>
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
@@ -18768,12 +18824,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0125 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0124 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a timing requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -18788,7 +18844,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P249" t="inlineStr"/>
@@ -18798,12 +18854,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0126</t>
+          <t>DDS_STBIO1_0125</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0126</t>
+          <t>DDS_STBIO1_0125</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -18814,7 +18870,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>• The user shall select active channel, in this case ECG0_SEL, BIA_SEL and DS_SEL (Data Storage Mode) in DEVICE_CONFIG_CHANNEL writing 0x23. [TO: IPOS_MAIN_CTRL]</t>
+          <t>[DDS_STBIO1_0125] Requirement: • The user shall configure the time slot duration in DEVICE_CONFIG_OPERATION register [4:2].</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -18824,7 +18880,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Section 2 SELECT CHANNEL: (under Section 15.3.2 ECG and BIA), paragraph 016 (page 150)</t>
+          <t>Section 1 TIME SLOT LENGTH: (under Section 15.3.2 ECG and BIA), paragraph 012 (page 150)</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
@@ -18840,12 +18896,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0126 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0125 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a timing requirement.</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -18860,7 +18916,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="P250" t="inlineStr"/>
@@ -18870,12 +18926,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0127</t>
+          <t>DDS_STBIO1_0126</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0127</t>
+          <t>DDS_STBIO1_0126</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -18886,7 +18942,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>• The user shall select a division index for ECG, configuring M_ECG_l and M_ECG_h in SET_ECG_FREQ_l register and SET_ECG_FREQ_h register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall select active channel, in this case ECG0_SEL, BIA_SEL and DS_SEL (Data Storage Mode) in DEVICE_CONFIG_CHANNEL writing 0x23. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -18896,7 +18952,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.2 ECG and BIA), paragraph 021 (page 150)</t>
+          <t>Section 2 SELECT CHANNEL: (under Section 15.3.2 ECG and BIA), paragraph 016 (page 150)</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
@@ -18912,7 +18968,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0127 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0126 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18942,12 +18998,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0128</t>
+          <t>DDS_STBIO1_0127</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0128</t>
+          <t>DDS_STBIO1_0127</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -18958,7 +19014,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>• The user shall select a division index for ECG, configuring M_BIA_l and M_BIA_h in SET_BIA_FREQ_l register and SET_BIA_FREQ_h register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall select a division index for ECG, configuring M_ECG_l and M_ECG_h in SET_ECG_FREQ_l register and SET_ECG_FREQ_h register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -18968,7 +19024,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.2 ECG and BIA), paragraph 025 (page 150)</t>
+          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.2 ECG and BIA), paragraph 021 (page 150)</t>
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
@@ -18984,7 +19040,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0128 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0127 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -19014,12 +19070,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0129</t>
+          <t>DDS_STBIO1_0128</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0129</t>
+          <t>DDS_STBIO1_0128</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -19030,7 +19086,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>• The user shall set number of clocks for sampling ECG and BIA data from ADC in ADC_CONFIG_ECG register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall select a division index for ECG, configuring M_BIA_l and M_BIA_h in SET_BIA_FREQ_l register and SET_BIA_FREQ_h register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -19040,7 +19096,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Section 4 CONFIGURE ADC SAMPLING PERIOD: (under Section 15.3.2 ECG and BIA), paragraph 029 (page 150)</t>
+          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.2 ECG and BIA), paragraph 025 (page 150)</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
@@ -19056,7 +19112,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0129 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0128 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19076,7 +19132,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P253" t="inlineStr"/>
@@ -19086,12 +19142,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0130</t>
+          <t>DDS_STBIO1_0129</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0130</t>
+          <t>DDS_STBIO1_0129</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -19102,7 +19158,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>• The user shall set at 1 HC_EN in ECG_CTRL register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall set number of clocks for sampling ECG and BIA data from ADC in ADC_CONFIG_ECG register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -19112,7 +19168,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Section 5 GENERAL CONFIG: (under Section 15.3.2 ECG and BIA), paragraph 033 (page 150)</t>
+          <t>Section 4 CONFIGURE ADC SAMPLING PERIOD: (under Section 15.3.2 ECG and BIA), paragraph 029 (page 150)</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
@@ -19128,7 +19184,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0130 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0129 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19148,7 +19204,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P254" t="inlineStr"/>
@@ -19158,12 +19214,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0140</t>
+          <t>DDS_STBIO1_0130</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0140</t>
+          <t>DDS_STBIO1_0130</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -19174,7 +19230,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>• The user shall set at 1 IMP_EN in IMP_CTRL register. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall set at 1 HC_EN in ECG_CTRL register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -19184,7 +19240,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Section 5 GENERAL CONFIG: (under Section 15.3.2 ECG and BIA), paragraph 036 (page 150)</t>
+          <t>Section 5 GENERAL CONFIG: (under Section 15.3.2 ECG and BIA), paragraph 033 (page 150)</t>
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
@@ -19200,7 +19256,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0140 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0130 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19230,12 +19286,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0141</t>
+          <t>DDS_STBIO1_0140</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0141</t>
+          <t>DDS_STBIO1_0140</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -19246,7 +19302,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>• The user shall start measurement writing register DEVICE_CONFIG_OPERATION [0] at 1. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall set at 1 IMP_EN in IMP_CTRL register. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -19256,7 +19312,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Section 6 SELECT OPERATIVE MODE: (under Section 15.3.2 ECG and BIA), paragraph 040 (page 150)</t>
+          <t>Section 5 GENERAL CONFIG: (under Section 15.3.2 ECG and BIA), paragraph 036 (page 150)</t>
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
@@ -19272,7 +19328,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0141 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0140 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19292,7 +19348,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P256" t="inlineStr"/>
@@ -19302,12 +19358,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0142</t>
+          <t>DDS_STBIO1_0141</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0142</t>
+          <t>DDS_STBIO1_0141</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -19318,7 +19374,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>• To check data in unique FIFO (default config) the user shall check the first MSB which will have to be equal to the one described in the DATA TAG Table. [TO: IPOS_MAIN_CTRL]</t>
+          <t>• The user shall start measurement writing register DEVICE_CONFIG_OPERATION [0] at 1. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -19328,7 +19384,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Section 7 CHECK DATA: (under Section 15.3.2 ECG and BIA), paragraph 044 (page 150)</t>
+          <t>Section 6 SELECT OPERATIVE MODE: (under Section 15.3.2 ECG and BIA), paragraph 040 (page 150)</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
@@ -19344,7 +19400,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0142 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0141 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19364,7 +19420,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P257" t="inlineStr"/>
@@ -19374,12 +19430,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0143</t>
+          <t>DDS_STBIO1_0142</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0143</t>
+          <t>DDS_STBIO1_0142</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -19390,7 +19446,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0143] Requirement: • The User shall configure time slot duration in DEVICE_CONFIG_OPERATION register [4:2].</t>
+          <t>• To check data in unique FIFO (default config) the user shall check the first MSB which will have to be equal to the one described in the DATA TAG Table. [TO: IPOS_MAIN_CTRL]</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -19400,7 +19456,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Section 1 TIME SLOT LENGTH: (under Section 15.3.3 PPG Only), paragraph 010 (page 152)</t>
+          <t>Section 7 CHECK DATA: (under Section 15.3.2 ECG and BIA), paragraph 044 (page 150)</t>
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
@@ -19416,12 +19472,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0143 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0142 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a timing requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -19436,7 +19492,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P258" t="inlineStr"/>
@@ -19446,12 +19502,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0145</t>
+          <t>DDS_STBIO1_0143</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0145</t>
+          <t>DDS_STBIO1_0143</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -19462,7 +19518,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0145] Requirement: • The user shall configure a division index PPG, writing M_PPG_l and M_PPG_h in SET_PPG_FREQ_l register and SET_PPG_FREQ_h register.</t>
+          <t>[DDS_STBIO1_0143] Requirement: • The User shall configure time slot duration in DEVICE_CONFIG_OPERATION register [4:2].</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -19472,7 +19528,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.3 PPG Only), paragraph 018 (page 152)</t>
+          <t>Section 1 TIME SLOT LENGTH: (under Section 15.3.3 PPG Only), paragraph 010 (page 152)</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
@@ -19488,12 +19544,12 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0145 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0143 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Narrative sentence states device behavior classified as a timing requirement.</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -19508,7 +19564,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="P259" t="inlineStr"/>
@@ -19518,12 +19574,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0146</t>
+          <t>DDS_STBIO1_0145</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0146</t>
+          <t>DDS_STBIO1_0145</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -19534,7 +19590,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0146] Requirement: • The user shall configure the number of clocks for sampling PPG data from ADC in ADC_CONFIG_PPG register.</t>
+          <t>[DDS_STBIO1_0145] Requirement: • The user shall configure a division index PPG, writing M_PPG_l and M_PPG_h in SET_PPG_FREQ_l register and SET_PPG_FREQ_h register.</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -19544,7 +19600,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Section 4 CONFIGURE ADC SAMPLING PERIOD: (under Section 15.3.3 PPG Only), paragraph 022 (page 152)</t>
+          <t>Section 3 SELECT DIVISION INDEX FOR CONFIGURED CHANNELS: (under Section 15.3.3 PPG Only), paragraph 018 (page 152)</t>
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
@@ -19560,12 +19616,12 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0146 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0145 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a functional requirement.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -19580,7 +19636,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P260" t="inlineStr"/>
@@ -19590,12 +19646,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0144</t>
+          <t>DDS_STBIO1_0146</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0144</t>
+          <t>DDS_STBIO1_0146</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -19606,7 +19662,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>• The user shall select active channel, in this case only PPG_SEL and DS_SEL (data Storage) in DEVICE_CONFIG_CHANNEL register shall be set to 0x30.</t>
+          <t>[DDS_STBIO1_0146] Requirement: • The user shall configure the number of clocks for sampling PPG data from ADC in ADC_CONFIG_PPG register.</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -19616,7 +19672,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Section 2 SELECT CHANNEL: (under Section 15.3.3 PPG Only), paragraph 014 (page 152)</t>
+          <t>Section 4 CONFIGURE ADC SAMPLING PERIOD: (under Section 15.3.3 PPG Only), paragraph 022 (page 152)</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
@@ -19632,12 +19688,12 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0144 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0146 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a functional requirement.</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -19652,7 +19708,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P261" t="inlineStr"/>
@@ -19662,12 +19718,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0147</t>
+          <t>DDS_STBIO1_0144</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0147</t>
+          <t>DDS_STBIO1_0144</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -19678,7 +19734,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>The user shall configure each frame following these steps: 5.1 ALC PARAMETERS: • T1 in PPG_ALC_CONFIG_PARAM_1 register. • T2, GAIN_START_SET, GAIN_MAX_SET in PPG_ALC_CONFIG_PARAM_2 register. 5.2 DIGITAL RAMP PARAMETERS: • N_MAX, T_DELTA in DIGITAL_RAMP_CONFIG_PARAM_1 register. • DELTA, T_DELTA1 in DIGITAL_RAMP_CONFIG_PARAM_2 register. • DELTA1 in DIGITAL_RAMP_CONFIG_PARAM_3 register. 5.3 GENERAL PPG PARAMETERS: • N_PPG_FRAME, WAVE_VELOCITY_MODE, SEL_PPG_ELAB in GENERAL_PPG_PARAMETERS_1 register. • T_TX_STARTUP in GENERAL_PPG_PARAMETERS_2 register. • T_RX_SET, PPG_START_UP_TIME_l in GENERAL_PPG_PARAMETERS_3 register. • PPG_START_UP_TIME_h in GENERAL_PPG_PARAMETERS_4 register. 5.4 PARAMETERS FOR EACH FRAME CONFIGURED BY USER: • RX_CH_FRAME_{n}, FRAME_{n}_SAMPLES, FRAME_{n}_REPETITION in FRAME_n_PARAMETERS_1 register. • BTIA_GAIN_FRAME_{n}, TX_LEDSET_FRAME_l_{n} in FRAME_n_PARAMETERS_2 register. • TX_LEDSET_FRAME_h_{n}, TX_LEDOFF_FRAME_l_{n} in FRAME_n_PARAMETERS_3 register. • TX_LEDOFF_FRAME_h_{n} in FRAME_n_PARAMETERS_4 register. • IDAC_DC_PPG_FRAME_{n} in FRAME_n_PARAMETERS_5 register. • EN_TX_i in FRAME_n_PARAMETERS_6 register. • CURR_SEL_TX_FRAME{n} in FRAME_n_PARAMETERS_7 register. • TX1_OUTAB_SEL_FRAME_{n}, TX2_OUTAB_SEL_FRAME_{n}, TX3_OUTAB_SEL_FRAME_{n}, TX4_OUTAB_SEL_FRAME_{n} in FRAME_n_PARAMETERS_10 register.</t>
+          <t>• The user shall select active channel, in this case only PPG_SEL and DS_SEL (data Storage) in DEVICE_CONFIG_CHANNEL register shall be set to 0x30.</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -19688,7 +19744,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Section 5 PPG FRAMES CONFIG: (under Section 15.3.3 PPG Only), paragraph 026 (page 152)</t>
+          <t>Section 2 SELECT CHANNEL: (under Section 15.3.3 PPG Only), paragraph 014 (page 152)</t>
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
@@ -19704,7 +19760,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0147 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:partial_overlap=0.76</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0144 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19728,22 +19784,18 @@
         </is>
       </c>
       <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
+      <c r="Q262" t="inlineStr"/>
       <c r="R262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0148</t>
+          <t>DDS_STBIO1_0147</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0148</t>
+          <t>DDS_STBIO1_0147</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -19754,7 +19806,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>[DDS_STBIO1_0148] Requirement: • The user shall write DEVICE_CONFIG_OPERATION register [0] at 1.</t>
+          <t>The user shall configure each frame following these steps: 5.1 ALC PARAMETERS: • T1 in PPG_ALC_CONFIG_PARAM_1 register. • T2, GAIN_START_SET, GAIN_MAX_SET in PPG_ALC_CONFIG_PARAM_2 register. 5.2 DIGITAL RAMP PARAMETERS: • N_MAX, T_DELTA in DIGITAL_RAMP_CONFIG_PARAM_1 register. • DELTA, T_DELTA1 in DIGITAL_RAMP_CONFIG_PARAM_2 register. • DELTA1 in DIGITAL_RAMP_CONFIG_PARAM_3 register. 5.3 GENERAL PPG PARAMETERS: • N_PPG_FRAME, WAVE_VELOCITY_MODE, SEL_PPG_ELAB in GENERAL_PPG_PARAMETERS_1 register. • T_TX_STARTUP in GENERAL_PPG_PARAMETERS_2 register. • T_RX_SET, PPG_START_UP_TIME_l in GENERAL_PPG_PARAMETERS_3 register. • PPG_START_UP_TIME_h in GENERAL_PPG_PARAMETERS_4 register. 5.4 PARAMETERS FOR EACH FRAME CONFIGURED BY USER: • RX_CH_FRAME_{n}, FRAME_{n}_SAMPLES, FRAME_{n}_REPETITION in FRAME_n_PARAMETERS_1 register. • BTIA_GAIN_FRAME_{n}, TX_LEDSET_FRAME_l_{n} in FRAME_n_PARAMETERS_2 register. • TX_LEDSET_FRAME_h_{n}, TX_LEDOFF_FRAME_l_{n} in FRAME_n_PARAMETERS_3 register. • TX_LEDOFF_FRAME_h_{n} in FRAME_n_PARAMETERS_4 register. • IDAC_DC_PPG_FRAME_{n} in FRAME_n_PARAMETERS_5 register. • EN_TX_i in FRAME_n_PARAMETERS_6 register. • CURR_SEL_TX_FRAME{n} in FRAME_n_PARAMETERS_7 register. • TX1_OUTAB_SEL_FRAME_{n}, TX2_OUTAB_SEL_FRAME_{n}, TX3_OUTAB_SEL_FRAME_{n}, TX4_OUTAB_SEL_FRAME_{n} in FRAME_n_PARAMETERS_10 register.</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -19764,7 +19816,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Section 6 SELECT OPERATIVE MODE: (under Section 15.3.3 PPG Only), paragraph 008 (page 153)</t>
+          <t>Section 5 PPG FRAMES CONFIG: (under Section 15.3.3 PPG Only), paragraph 026 (page 152)</t>
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
@@ -19780,12 +19832,12 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0148 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0147 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:partial_overlap=0.76</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Narrative sentence states device behavior classified as a other requirement.</t>
+          <t>Source requirement ID was preserved from the specification text.</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -19804,18 +19856,22 @@
         </is>
       </c>
       <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>LED</t>
+        </is>
+      </c>
       <c r="R263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0149</t>
+          <t>DDS_STBIO1_0148</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0149</t>
+          <t>DDS_STBIO1_0148</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -19826,7 +19882,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>• To check data in unique FIFO (default config) the user shall check the first MSB. PPG DATA has 20 bits of data and 4 of TAG. The 4 bits, from 0 to 11, are used to identify the frame (as described in the table in DATA TAG table).</t>
+          <t>[DDS_STBIO1_0148] Requirement: • The user shall write DEVICE_CONFIG_OPERATION register [0] at 1.</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -19836,7 +19892,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Section 7 CHECK DATA: (under Section 15.3.3 PPG Only), paragraph 011 (page 153)</t>
+          <t>Section 6 SELECT OPERATIVE MODE: (under Section 15.3.3 PPG Only), paragraph 008 (page 153)</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
@@ -19852,12 +19908,12 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0149 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR functional sentence using ontology rule | source_req_id=DDS_STBIO1_0148 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>Source requirement ID was preserved from the specification text.</t>
+          <t>Narrative sentence states device behavior classified as a other requirement.</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -19877,21 +19933,17 @@
       </c>
       <c r="P264" t="inlineStr"/>
       <c r="Q264" t="inlineStr"/>
-      <c r="R264" t="inlineStr">
-        <is>
-          <t>20 bits; 4 bits</t>
-        </is>
-      </c>
+      <c r="R264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0699</t>
+          <t>DDS_STBIO1_0149</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0699</t>
+          <t>DDS_STBIO1_0149</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -19902,7 +19954,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>After the initial boot phase, only with SPI interface, to turn on the Scan mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x01) Figure 26 scan mode activation timing</t>
+          <t>• To check data in unique FIFO (default config) the user shall check the first MSB. PPG DATA has 20 bits of data and 4 of TAG. The 4 bits, from 0 to 11, are used to identify the frame (as described in the table in DATA TAG table). Figure 24: PPG Measurement Flowchart</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -19912,7 +19964,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Section 18.1 Scan mode (under Section 18 Digital DFT), paragraph 011 (page 159)</t>
+          <t>Section 7 CHECK DATA: (under Section 15.3.3 PPG Only), paragraph 011 (page 153)</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
@@ -19928,7 +19980,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0699 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.90</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0149 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.89</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19948,22 +20000,26 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P265" t="inlineStr"/>
       <c r="Q265" t="inlineStr"/>
-      <c r="R265" t="inlineStr"/>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>20 bits; 4 bits</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0700</t>
+          <t>DDS_STBIO1_0699</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0700</t>
+          <t>DDS_STBIO1_0699</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -19974,7 +20030,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>After the initial boot phase, to turn on the Debug mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x08)</t>
+          <t>After the initial boot phase, only with SPI interface, to turn on the Scan mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x01) Figure 26 scan mode activation timing</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -19984,7 +20040,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Section 18.2 Debug mode (under Section 18 Digital DFT), paragraph 024 (page 159)</t>
+          <t>Section 18.1 Scan mode (under Section 18 Digital DFT), paragraph 011 (page 159)</t>
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
@@ -20000,7 +20056,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0700 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0699 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.90</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -20020,7 +20076,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="P266" t="inlineStr"/>
@@ -20030,12 +20086,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0701</t>
+          <t>DDS_STBIO1_0700</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0701</t>
+          <t>DDS_STBIO1_0700</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -20046,7 +20102,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>To turn on the ADC TEST LOW NOISE mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0xF, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable ADC in debug mode (ADDRESS=0x09, DATA=0x06) • Select page 2 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable ADC TEST LOW NOISE and input of ADC from GPIO (ADDRESS=0x0A, DATA=0x14) • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x08)</t>
+          <t>After the initial boot phase, to turn on the Debug mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x08)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -20056,7 +20112,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Section 18.3 ADC TEST LOW NOISE (under Section 18 Digital DFT), paragraph 006 (page 160)</t>
+          <t>Section 18.2 Debug mode (under Section 18 Digital DFT), paragraph 024 (page 159)</t>
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
@@ -20072,7 +20128,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0701 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0700 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20092,7 +20148,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P267" t="inlineStr"/>
@@ -20102,12 +20158,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0702</t>
+          <t>DDS_STBIO1_0701</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0702</t>
+          <t>DDS_STBIO1_0701</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -20128,7 +20184,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Section 18.3 ADC TEST LOW NOISE (under Section 18 Digital DFT), paragraph 023 (page 160)</t>
+          <t>Section 18.3 ADC TEST LOW NOISE (under Section 18 Digital DFT), paragraph 006 (page 160)</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
@@ -20144,7 +20200,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0702 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0701 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20174,12 +20230,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_1507</t>
+          <t>DDS_STBIO1_0702</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_1507</t>
+          <t>DDS_STBIO1_0702</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -20190,7 +20246,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>To turn on the ADC TEST LOW NOISE mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0xF, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable ADC in debug mode (ADDRESS=0x09, DATA=0x06) • Select page 2 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable ADC TEST LOW NOISE and input of ADC from GPIO (ADDRESS=0x0A, DATA=0x0C) • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x08)</t>
+          <t>To turn on the ADC TEST LOW NOISE mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0xF, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable ADC in debug mode (ADDRESS=0x09, DATA=0x06) • Select page 2 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable ADC TEST LOW NOISE and input of ADC from GPIO (ADDRESS=0x0A, DATA=0x14) • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x08)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -20200,7 +20256,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Section 18.4 ADC TEST FAST (under Section 18 Digital DFT), paragraph 010 (page 161)</t>
+          <t>Section 18.3 ADC TEST LOW NOISE (under Section 18 Digital DFT), paragraph 023 (page 160)</t>
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
@@ -20216,7 +20272,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_1507 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_0702 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20246,12 +20302,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_2507</t>
+          <t>DDS_STBIO1_1507</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_2507</t>
+          <t>DDS_STBIO1_1507</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -20262,7 +20318,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>After the initial boot phase, to turn on the Debug mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable the power island [DDS_STBIO1_0507] • Enable bist mode by writing to regmap (ADDRESS=0x3E, DATA=0x04)</t>
+          <t>To turn on the ADC TEST LOW NOISE mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0xF, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable ADC in debug mode (ADDRESS=0x09, DATA=0x06) • Select page 2 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable ADC TEST LOW NOISE and input of ADC from GPIO (ADDRESS=0x0A, DATA=0x0C) • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x02) • Enable debug mode by writing to regmap (ADDRESS=0x3E, DATA=0x08)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -20272,7 +20328,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Section 18.5 BIST MODE (under Section 18 Digital DFT), paragraph 030 (page 161)</t>
+          <t>Section 18.4 ADC TEST FAST (under Section 18 Digital DFT), paragraph 010 (page 161)</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
@@ -20288,7 +20344,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_2507 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.89</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_1507 | id_policy=preserve_tagged_source_id | rag_crosscheck=ok:exact_match</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20308,7 +20364,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="P270" t="inlineStr"/>
@@ -20318,12 +20374,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0013</t>
+          <t>DDS_STBIO1_2507</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_0013</t>
+          <t>DDS_STBIO1_2507</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -20334,7 +20390,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>To move OTP signal, ADSP shall write a new value in a regbank by AHB protocol.</t>
+          <t>After the initial boot phase, to turn on the Debug mode shall be: • Select page 3 of the regmap (ADDRESS=0x40, DATA=0x03) • Enable LDO 1V8 by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x02) • Enable clock by writing to regmap VIREF_LDO1V8_CLK16M register (ADDRESS=0x0F, DATA=0x12) • Enable the power island [DDS_STBIO1_0507] • Enable bist mode by writing to regmap (ADDRESS=0x3E, DATA=0x04)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -20344,14 +20400,10 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 039 (page 89)</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>ADSP</t>
-        </is>
-      </c>
+          <t>Section 18.5 BIST MODE (under Section 18 Digital DFT), paragraph 030 (page 161)</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>raw</t>
@@ -20364,7 +20416,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>User-approved recovery of source-tagged requirement omitted by OCR table parsing. | table_line_info=page89:lines[039] | source_req_id=DDS_STBIO1_0013 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=1.00</t>
+          <t>Auto-extracted from OCR normative statement | source_req_id=DDS_STBIO1_2507 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=0.89</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20384,7 +20436,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>electrical</t>
         </is>
       </c>
       <c r="P271" t="inlineStr"/>
@@ -20394,12 +20446,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_395</t>
+          <t>DDS_STBIO1_0013</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DDS_STBIO1_395</t>
+          <t>DDS_STBIO1_0013</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -20410,22 +20462,22 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>The DCC feature consists of two stages that detect whether one of six electrode inputs is in the range 0 to 1.5V; thresholds have a 100mV step, and continuous current from 25nA to 200nA flows from the stages into the electrodes.</t>
+          <t>To move OTP signal, ADSP shall write a new value in a regbank by AHB protocol.</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Analog</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Section 13.1.2.2 Requirements (under Section 13.1.2 PAD Mux), paragraph 033 (page 71)</t>
+          <t>Section 13.2.1.1.2 Requirements (under Section 13.2.1.1 ADSP Peculiar Requirements), paragraph 039 (page 89)</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>PAD MUX</t>
+          <t>ADSP</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -20440,7 +20492,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>User-approved recovery of source-tagged requirement omitted by OCR table parsing. | table_line_info=page71:lines[033] | source_req_id=DDS_STBIO1_395 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:partial_overlap=0.79</t>
+          <t>User-approved recovery of source-tagged requirement omitted by OCR table parsing. | table_line_info=page89:lines[039] | source_req_id=DDS_STBIO1_0013 | id_policy=preserve_tagged_source_id | rag_crosscheck=warn:high_overlap=1.00</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20460,16 +20512,12 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>electrical</t>
+          <t>other</t>
         </is>
       </c>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
-      <c r="R272" t="inlineStr">
-        <is>
-          <t>1.5V</t>
-        </is>
-      </c>
+      <c r="R272" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20521,7 +20569,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T14:14:41+00:00</t>
+          <t>2026-10-13T18:27:31+00:00</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20581,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>snap-b2e8101b00dc6909feaed885</t>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20593,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>b2e8101b00dc6909feaed8858c8391a595fd7fe52538e9b17b233477d99c8a6d</t>
+          <t>0c71eaa9e10d8478c2ac3726113d42cead2cf039a4bd64b4fab7e6c9dc116eac</t>
         </is>
       </c>
     </row>
@@ -20557,7 +20605,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\data\canonical\canonical_store.sqlite</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\data\canonical\canonical_store.sqlite</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20617,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\traceability_reports\primary_source_requirements.xlsx</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\traceability_reports\primary_source_requirements.xlsx</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20651,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\STBIO_AI\artifacts\stage1_requirements\requirements_summary.csv</t>
+          <t>C:\Users\iannuzza\LOCAL_PROJ\Github_copilot_proj\Deterministic_Reqs_workflow\artifacts\stage1_requirements\requirements_summary.csv</t>
         </is>
       </c>
     </row>
@@ -20622,4 +20670,999 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>covering_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>covering_block</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_block</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>denominator_scope</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>covered_unique_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>total_unique_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>uncovered_upstream_requirements</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_percentage</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_basis</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_requirement_ids</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>uncovered_upstream_requirement_ids</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_id</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>covering_node_id</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>covered_upstream_node_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>55</v>
+      </c>
+      <c r="G2" t="n">
+        <v>357</v>
+      </c>
+      <c r="H2" t="n">
+        <v>302</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>15.40616246498599</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Unique upstream IDs resolved by central approved Covers contract; not publication gate status</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0032;DDS_STBIO1_0036;DDS_STBIO1_0116;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2507;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>DRS</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADSP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" t="n">
+        <v>357</v>
+      </c>
+      <c r="H3" t="n">
+        <v>338</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>5.322128851540616</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0032;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:adsp</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>I2C_SPI_AHB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>357</v>
+      </c>
+      <c r="H4" t="n">
+        <v>342</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>4.201680672268908</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:i2c-spi-ahb</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Main Controller</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>181</v>
+      </c>
+      <c r="G5" t="n">
+        <v>357</v>
+      </c>
+      <c r="H5" t="n">
+        <v>176</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>50.70028011204482</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:main-controller</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pad Mux</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>357</v>
+      </c>
+      <c r="H6" t="n">
+        <v>340</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4.761904761904762</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:pad-mux</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PMU</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>31</v>
+      </c>
+      <c r="G7" t="n">
+        <v>357</v>
+      </c>
+      <c r="H7" t="n">
+        <v>326</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>8.683473389355742</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:pmu</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Regmap</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>357</v>
+      </c>
+      <c r="H8" t="n">
+        <v>349</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>2.240896358543417</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_4000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:regmap</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sensor-Hub</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>18</v>
+      </c>
+      <c r="G9" t="n">
+        <v>357</v>
+      </c>
+      <c r="H9" t="n">
+        <v>339</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.042016806722689</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:sensor-hub</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Digital IPOS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Smart FIFO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>357</v>
+      </c>
+      <c r="H10" t="n">
+        <v>344</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3.641456582633054</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500;IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Digital_IPOS:smart-fifo</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supplementary specification: IPOS_MAIN_CTRL.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Primary source specification: dds_stbio1.pdf</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Approved source ledger</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>166</v>
+      </c>
+      <c r="G11" t="n">
+        <v>357</v>
+      </c>
+      <c r="H11" t="n">
+        <v>191</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>46.49859943977591</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Central source-spec provenance/trace ID coverage; not generated-document Covers or publication gate status</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>IPOS_STBIO1_MAIN_CONTROLLER_002;IPOS_STBIO1_MAIN_CONTROLLER_004;IPOS_STBIO1_MAIN_CONTROLLER_008;IPOS_STBIO1_MAIN_CONTROLLER_009;IPOS_STBIO1_MAIN_CONTROLLER_010;IPOS_STBIO1_MAIN_CONTROLLER_011;IPOS_STBIO1_MAIN_CONTROLLER_015;IPOS_STBIO1_MAIN_CONTROLLER_0152;IPOS_STBIO1_MAIN_CONTROLLER_016;IPOS_STBIO1_MAIN_CONTROLLER_017;IPOS_STBIO1_MAIN_CONTROLLER_018;IPOS_STBIO1_MAIN_CONTROLLER_019;IPOS_STBIO1_MAIN_CONTROLLER_020;IPOS_STBIO1_MAIN_CONTROLLER_021;IPOS_STBIO1_MAIN_CONTROLLER_022;IPOS_STBIO1_MAIN_CONTROLLER_023;IPOS_STBIO1_MAIN_CONTROLLER_024;IPOS_STBIO1_MAIN_CONTROLLER_026;IPOS_STBIO1_MAIN_CONTROLLER_027;IPOS_STBIO1_MAIN_CONTROLLER_028;IPOS_STBIO1_MAIN_CONTROLLER_029;IPOS_STBIO1_MAIN_CONTROLLER_030;IPOS_STBIO1_MAIN_CONTROLLER_031;IPOS_STBIO1_MAIN_CONTROLLER_032;IPOS_STBIO1_MAIN_CONTROLLER_033;IPOS_STBIO1_MAIN_CONTROLLER_034;IPOS_STBIO1_MAIN_CONTROLLER_035;IPOS_STBIO1_MAIN_CONTROLLER_036;IPOS_STBIO1_MAIN_CONTROLLER_037;IPOS_STBIO1_MAIN_CONTROLLER_038;IPOS_STBIO1_MAIN_CONTROLLER_039;IPOS_STBIO1_MAIN_CONTROLLER_040;IPOS_STBIO1_MAIN_CONTROLLER_043;IPOS_STBIO1_MAIN_CONTROLLER_044;IPOS_STBIO1_MAIN_CONTROLLER_045;IPOS_STBIO1_MAIN_CONTROLLER_047;IPOS_STBIO1_MAIN_CONTROLLER_048;IPOS_STBIO1_MAIN_CONTROLLER_049;IPOS_STBIO1_MAIN_CONTROLLER_051;IPOS_STBIO1_MAIN_CONTROLLER_052;IPOS_STBIO1_MAIN_CONTROLLER_053;IPOS_STBIO1_MAIN_CONTROLLER_054;IPOS_STBIO1_MAIN_CONTROLLER_055;IPOS_STBIO1_MAIN_CONTROLLER_058;IPOS_STBIO1_MAIN_CONTROLLER_059;IPOS_STBIO1_MAIN_CONTROLLER_060;IPOS_STBIO1_MAIN_CONTROLLER_061;IPOS_STBIO1_MAIN_CONTROLLER_062;IPOS_STBIO1_MAIN_CONTROLLER_063;IPOS_STBIO1_MAIN_CONTROLLER_064;IPOS_STBIO1_MAIN_CONTROLLER_072;IPOS_STBIO1_MAIN_CONTROLLER_073;IPOS_STBIO1_MAIN_CONTROLLER_074;IPOS_STBIO1_MAIN_CONTROLLER_075;IPOS_STBIO1_MAIN_CONTROLLER_076;IPOS_STBIO1_MAIN_CONTROLLER_077;IPOS_STBIO1_MAIN_CONTROLLER_078;IPOS_STBIO1_MAIN_CONTROLLER_080;IPOS_STBIO1_MAIN_CONTROLLER_081;IPOS_STBIO1_MAIN_CONTROLLER_082;IPOS_STBIO1_MAIN_CONTROLLER_083;IPOS_STBIO1_MAIN_CONTROLLER_084;IPOS_STBIO1_MAIN_CONTROLLER_085;IPOS_STBIO1_MAIN_CONTROLLER_086;IPOS_STBIO1_MAIN_CONTROLLER_087;IPOS_STBIO1_MAIN_CONTROLLER_088;IPOS_STBIO1_MAIN_CONTROLLER_089;IPOS_STBIO1_MAIN_CONTROLLER_090;IPOS_STBIO1_MAIN_CONTROLLER_092;IPOS_STBIO1_MAIN_CONTROLLER_093;IPOS_STBIO1_MAIN_CONTROLLER_094;IPOS_STBIO1_MAIN_CONTROLLER_095;IPOS_STBIO1_MAIN_CONTROLLER_096;IPOS_STBIO1_MAIN_CONTROLLER_097;IPOS_STBIO1_MAIN_CONTROLLER_098;IPOS_STBIO1_MAIN_CONTROLLER_099;IPOS_STBIO1_MAIN_CONTROLLER_100;IPOS_STBIO1_MAIN_CONTROLLER_1004;IPOS_STBIO1_MAIN_CONTROLLER_1005;IPOS_STBIO1_MAIN_CONTROLLER_1007;IPOS_STBIO1_MAIN_CONTROLLER_1008;IPOS_STBIO1_MAIN_CONTROLLER_1009;IPOS_STBIO1_MAIN_CONTROLLER_101;IPOS_STBIO1_MAIN_CONTROLLER_1010;IPOS_STBIO1_MAIN_CONTROLLER_1011;IPOS_STBIO1_MAIN_CONTROLLER_102;IPOS_STBIO1_MAIN_CONTROLLER_103;IPOS_STBIO1_MAIN_CONTROLLER_1034;IPOS_STBIO1_MAIN_CONTROLLER_104;IPOS_STBIO1_MAIN_CONTROLLER_105;IPOS_STBIO1_MAIN_CONTROLLER_106;IPOS_STBIO1_MAIN_CONTROLLER_107;IPOS_STBIO1_MAIN_CONTROLLER_108;IPOS_STBIO1_MAIN_CONTROLLER_109;IPOS_STBIO1_MAIN_CONTROLLER_1095;IPOS_STBIO1_MAIN_CONTROLLER_110;IPOS_STBIO1_MAIN_CONTROLLER_1102;IPOS_STBIO1_MAIN_CONTROLLER_1104;IPOS_STBIO1_MAIN_CONTROLLER_1105;IPOS_STBIO1_MAIN_CONTROLLER_111;IPOS_STBIO1_MAIN_CONTROLLER_1116;IPOS_STBIO1_MAIN_CONTROLLER_1118;IPOS_STBIO1_MAIN_CONTROLLER_1119;IPOS_STBIO1_MAIN_CONTROLLER_112;IPOS_STBIO1_MAIN_CONTROLLER_113;IPOS_STBIO1_MAIN_CONTROLLER_1136;IPOS_STBIO1_MAIN_CONTROLLER_1139;IPOS_STBIO1_MAIN_CONTROLLER_1143;IPOS_STBIO1_MAIN_CONTROLLER_115;IPOS_STBIO1_MAIN_CONTROLLER_118;IPOS_STBIO1_MAIN_CONTROLLER_120;IPOS_STBIO1_MAIN_CONTROLLER_121;IPOS_STBIO1_MAIN_CONTROLLER_122;IPOS_STBIO1_MAIN_CONTROLLER_123;IPOS_STBIO1_MAIN_CONTROLLER_124;IPOS_STBIO1_MAIN_CONTROLLER_125;IPOS_STBIO1_MAIN_CONTROLLER_126;IPOS_STBIO1_MAIN_CONTROLLER_127;IPOS_STBIO1_MAIN_CONTROLLER_128;IPOS_STBIO1_MAIN_CONTROLLER_129;IPOS_STBIO1_MAIN_CONTROLLER_132;IPOS_STBIO1_MAIN_CONTROLLER_133;IPOS_STBIO1_MAIN_CONTROLLER_134;IPOS_STBIO1_MAIN_CONTROLLER_137;IPOS_STBIO1_MAIN_CONTROLLER_138;IPOS_STBIO1_MAIN_CONTROLLER_139;IPOS_STBIO1_MAIN_CONTROLLER_140;IPOS_STBIO1_MAIN_CONTROLLER_143;IPOS_STBIO1_MAIN_CONTROLLER_2117;IPOS_STBIO1_MAIN_CONTROLLER_2143;IPOS_STBIO1_MAIN_CONTROLLER_2144;IPOS_STBIO1_MAIN_CONTROLLER_2145;IPOS_STBIO1_MAIN_CONTROLLER_2146;IPOS_STBIO1_MAIN_CONTROLLER_300;IPOS_STBIO1_MAIN_CONTROLLER_3124;IPOS_STBIO1_MAIN_CONTROLLER_3125;IPOS_STBIO1_MAIN_CONTROLLER_3126;IPOS_STBIO1_MAIN_CONTROLLER_3127;IPOS_STBIO1_MAIN_CONTROLLER_3128;IPOS_STBIO1_MAIN_CONTROLLER_3129;IPOS_STBIO1_MAIN_CONTROLLER_3130;IPOS_STBIO1_MAIN_CONTROLLER_3131;IPOS_STBIO1_MAIN_CONTROLLER_4034;IPOS_STBIO1_MAIN_CONTROLLER_4079;IPOS_STBIO1_MAIN_CONTROLLER_4080;IPOS_STBIO1_MAIN_CONTROLLER_4090;IPOS_STBIO1_MAIN_CONTROLLER_4091;IPOS_STBIO1_MAIN_CONTROLLER_436;IPOS_STBIO1_MAIN_CONTROLLER_5004;IPOS_STBIO1_MAIN_CONTROLLER_5005;IPOS_STBIO1_MAIN_CONTROLLER_5015;IPOS_STBIO1_MAIN_CONTROLLER_5016;IPOS_STBIO1_MAIN_CONTROLLER_5080;IPOS_STBIO1_MAIN_CONTROLLER_5091;IPOS_STBIO1_MAIN_CONTROLLER_5092;IPOS_STBIO1_MAIN_CONTROLLER_6059;IPOS_STBIO1_MAIN_CONTROLLER_6070;IPOS_STBIO1_MAIN_CONTROLLER_6098;IPOS_STBIO1_MAIN_CONTROLLER_6129;IPOS_STBIO1_MAIN_CONTROLLER_7095;IPOS_STBIO1_MAIN_CONTROLLER_7135;IPOS_STBIO1_MAIN_CONTROLLER_728;IPOS_STBIO1_MAIN_CONTROLLER_8106;IPOS_STBIO1_MAIN_CONTROLLER_8116;IPOS_STBIO1_MAIN_CONTROLLER_9116;IPOS_STBIO1_MAIN_CONTROLLER_9139</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>DDS_STBIO1_00000008;DDS_STBIO1_00000102;DDS_STBIO1_00000199;DDS_STBIO1_00000202;DDS_STBIO1_00001199;DDS_STBIO1_0013;DDS_STBIO1_0014;DDS_STBIO1_0015;DDS_STBIO1_0016;DDS_STBIO1_0017;DDS_STBIO1_0018;DDS_STBIO1_0019;DDS_STBIO1_0020;DDS_STBIO1_0021;DDS_STBIO1_0022;DDS_STBIO1_0023;DDS_STBIO1_0024;DDS_STBIO1_0025;DDS_STBIO1_0026;DDS_STBIO1_0027;DDS_STBIO1_0028;DDS_STBIO1_0032;DDS_STBIO1_0033;DDS_STBIO1_0034;DDS_STBIO1_0035;DDS_STBIO1_0036;DDS_STBIO1_0104;DDS_STBIO1_0105;DDS_STBIO1_0106;DDS_STBIO1_0107;DDS_STBIO1_0108;DDS_STBIO1_0109;DDS_STBIO1_0110;DDS_STBIO1_0111;DDS_STBIO1_0112;DDS_STBIO1_0113;DDS_STBIO1_0114;DDS_STBIO1_0115;DDS_STBIO1_0116;DDS_STBIO1_0117;DDS_STBIO1_0118;DDS_STBIO1_0119;DDS_STBIO1_0120;DDS_STBIO1_0121;DDS_STBIO1_0122;DDS_STBIO1_0123;DDS_STBIO1_0124;DDS_STBIO1_0125;DDS_STBIO1_0126;DDS_STBIO1_0127;DDS_STBIO1_0128;DDS_STBIO1_0129;DDS_STBIO1_0130;DDS_STBIO1_0140;DDS_STBIO1_0141;DDS_STBIO1_0142;DDS_STBIO1_0143;DDS_STBIO1_0144;DDS_STBIO1_0145;DDS_STBIO1_0146;DDS_STBIO1_0147;DDS_STBIO1_0148;DDS_STBIO1_0149;DDS_STBIO1_0201;DDS_STBIO1_0202;DDS_STBIO1_0203;DDS_STBIO1_0204;DDS_STBIO1_0206;DDS_STBIO1_0207;DDS_STBIO1_0208;DDS_STBIO1_0209;DDS_STBIO1_0210;DDS_STBIO1_0211;DDS_STBIO1_0212;DDS_STBIO1_0213;DDS_STBIO1_0215;DDS_STBIO1_0216;DDS_STBIO1_0217;DDS_STBIO1_0218;DDS_STBIO1_0219;DDS_STBIO1_0220;DDS_STBIO1_0221;DDS_STBIO1_0222;DDS_STBIO1_0223;DDS_STBIO1_0501;DDS_STBIO1_05010;DDS_STBIO1_05011;DDS_STBIO1_0502;DDS_STBIO1_0503;DDS_STBIO1_0504;DDS_STBIO1_0505;DDS_STBIO1_0507;DDS_STBIO1_0508;DDS_STBIO1_0509;DDS_STBIO1_0699;DDS_STBIO1_0700;DDS_STBIO1_0701;DDS_STBIO1_0702;DDS_STBIO1_1020;DDS_STBIO1_1021;DDS_STBIO1_1022;DDS_STBIO1_1023;DDS_STBIO1_1024;DDS_STBIO1_1025;DDS_STBIO1_1026;DDS_STBIO1_1027;DDS_STBIO1_1050;DDS_STBIO1_1051;DDS_STBIO1_1052;DDS_STBIO1_1053;DDS_STBIO1_1054;DDS_STBIO1_1114;DDS_STBIO1_1507;DDS_STBIO1_2024;DDS_STBIO1_2025;DDS_STBIO1_2026;DDS_STBIO1_2052;DDS_STBIO1_2053;DDS_STBIO1_2054;DDS_STBIO1_2507;DDS_STBIO1_3000;DDS_STBIO1_3001;DDS_STBIO1_3002;DDS_STBIO1_3003;DDS_STBIO1_3004;DDS_STBIO1_3005;DDS_STBIO1_3006;DDS_STBIO1_302;DDS_STBIO1_303;DDS_STBIO1_304;DDS_STBIO1_305;DDS_STBIO1_306;DDS_STBIO1_307;DDS_STBIO1_308;DDS_STBIO1_309;DDS_STBIO1_310;DDS_STBIO1_311;DDS_STBIO1_312;DDS_STBIO1_313;DDS_STBIO1_314;DDS_STBIO1_392;DDS_STBIO1_393;DDS_STBIO1_394;DDS_STBIO1_395;DDS_STBIO1_4000;DDS_STBIO1_8000;DDS_STBIO1_8001;DDS_STBIO1_8002;DDS_STBIO1_8003;DDS_STBIO1_8004;DDS_STBIO1_8005;DDS_STBIO1_8006;DDS_STBIO1_8007;DDS_STBIO1_8100;DDS_STBIO1_8101;DDS_STBIO1_8102;DDS_STBIO1_8103;DDS_STBIO1_8104;DDS_STBIO1_8105;DDS_STBIO1_8106;DDS_STBIO1_89455232;DDS_STBIO1_89455261;DDS_STBIO1_89455449;DDS_STBIO1_89456557;DDS_STBIO1_89456975;DDS_STBIO1_89457435;DDS_STBIO1_89457790;DDS_STBIO1_89459082;DDS_STBIO1_9004;DDS_STBIO1_9011;DDS_STBIO1_9012;DDS_STBIO1_9013;DDS_STBIO1_9014;DDS_STBIO1_9017;DDS_STBIO1_9018;DDS_STBIO1_9024;DDS_STBIO1_9027;DDS_STBIO1_9029;DDS_STBIO1_9030;DDS_STBIO1_9031;DDS_STBIO1_9032;DDS_STBIO1_9033;DDS_STBIO1_9034;DDS_STBIO1_9035;DDS_STBIO1_9260;DDS_STBIO1_9261;DDS_STBIO1_9262;DDS_STBIO1_9263;DDS_STBIO1_9300;DDS_STBIO1_9317;DDS_STBIO1_9500</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>supplementary:ipos_main_ctrl.pdf</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>source:dds_stbio1.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="31" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>hierarchy_level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>expected_requirements</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>represented_requirements</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>missing_requirements</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>presence_percentage</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>presence_status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_basis</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>missing_requirement_ids</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Primary Source Requirements</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(All blocks)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Catalog total</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>271</v>
+      </c>
+      <c r="E2" t="n">
+        <v>191</v>
+      </c>
+      <c r="F2" t="n">
+        <v>80</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>70.47970479704797</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Source catalog IDs present in approved snapshot; not publication gate status</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CONF_SYS-RQ-030;CONF_SYS-RQ-039;CONF_SYS-RQ-052;CONF_SYS-RQ-056;CONF_SYS-RQ-057;CONF_SYS-RQ-058;CONF_SYS-RQ-059;CONF_SYS-RQ-063;CONF_SYS-RQ-077;REQ_DIG-RQ-001;REQ_SYS-RQ-001;REQ_SYS-RQ-002;REQ_SYS-RQ-003;REQ_SYS-RQ-004;REQ_SYS-RQ-005;REQ_SYS-RQ-006;REQ_SYS-RQ-007;REQ_SYS-RQ-008;REQ_SYS-RQ-009;REQ_SYS-RQ-010;REQ_SYS-RQ-011;REQ_SYS-RQ-012;REQ_SYS-RQ-013;REQ_SYS-RQ-014;REQ_SYS-RQ-015;REQ_SYS-RQ-016;REQ_SYS-RQ-017;REQ_SYS-RQ-018;REQ_SYS-RQ-019;REQ_SYS-RQ-020;REQ_SYS-RQ-021;REQ_SYS-RQ-022;REQ_SYS-RQ-023;REQ_SYS-RQ-024;REQ_SYS-RQ-025;REQ_SYS-RQ-026;REQ_SYS-RQ-027;REQ_SYS-RQ-028;REQ_SYS-RQ-029;REQ_SYS-RQ-031;REQ_SYS-RQ-032;REQ_SYS-RQ-033;REQ_SYS-RQ-034;REQ_SYS-RQ-035;REQ_SYS-RQ-036;REQ_SYS-RQ-037;REQ_SYS-RQ-038;REQ_SYS-RQ-040;REQ_SYS-RQ-041;REQ_SYS-RQ-042;REQ_SYS-RQ-043;REQ_SYS-RQ-044;REQ_SYS-RQ-045;REQ_SYS-RQ-046;REQ_SYS-RQ-047;REQ_SYS-RQ-048;REQ_SYS-RQ-049;REQ_SYS-RQ-050;REQ_SYS-RQ-051;REQ_SYS-RQ-053;REQ_SYS-RQ-054;REQ_SYS-RQ-055;REQ_SYS-RQ-060;REQ_SYS-RQ-061;REQ_SYS-RQ-062;REQ_SYS-RQ-064;REQ_SYS-RQ-065;REQ_SYS-RQ-066;REQ_SYS-RQ-067;REQ_SYS-RQ-068;REQ_SYS-RQ-069;REQ_SYS-RQ-070;REQ_SYS-RQ-071;REQ_SYS-RQ-072;REQ_SYS-RQ-073;REQ_SYS-RQ-074;REQ_SYS-RQ-075;REQ_SYS-RQ-076;REQ_SYS-RQ-078;REQ_SYS-RQ-079</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>snap-73c872b1307b6adb5eaf843e</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>